--- a/Program terapeuti Healthfest.xlsx
+++ b/Program terapeuti Healthfest.xlsx
@@ -271,7 +271,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,6 +282,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00FFFF"/>
         <bgColor rgb="FF00FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -335,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -420,8 +426,26 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1475,13 +1499,13 @@
       <c r="A28" s="5">
         <v>26.06</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="E28" s="5"/>
@@ -1537,13 +1561,13 @@
     </row>
     <row r="30">
       <c r="A30" s="19"/>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="31" t="s">
         <v>50</v>
       </c>
       <c r="E30" s="18"/>
@@ -1663,7 +1687,7 @@
       <c r="A34" s="5">
         <v>27.06</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="32" t="s">
         <v>54</v>
       </c>
       <c r="C34" s="5" t="s">
@@ -1780,16 +1804,16 @@
       <c r="W37" s="3"/>
     </row>
     <row r="38">
-      <c r="A38" s="5">
+      <c r="A38" s="29">
         <v>28.06</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E38" s="7"/>
@@ -1813,14 +1837,14 @@
       <c r="W38" s="3"/>
     </row>
     <row r="39">
-      <c r="A39" s="19"/>
-      <c r="B39" s="20" t="s">
+      <c r="A39" s="34"/>
+      <c r="B39" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="30" t="s">
         <v>61</v>
       </c>
       <c r="E39" s="21"/>
@@ -1968,13 +1992,13 @@
       <c r="W43" s="3"/>
     </row>
     <row r="44">
-      <c r="A44" s="29"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
@@ -1996,7 +2020,7 @@
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="33"/>
+      <c r="D45" s="39"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -2021,7 +2045,7 @@
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="33"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -2046,7 +2070,7 @@
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="33"/>
+      <c r="D47" s="39"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -2071,7 +2095,7 @@
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="33"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -2096,7 +2120,7 @@
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="33"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2121,7 +2145,7 @@
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="33"/>
+      <c r="D50" s="39"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -2146,7 +2170,7 @@
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="33"/>
+      <c r="D51" s="39"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -2171,7 +2195,7 @@
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="33"/>
+      <c r="D52" s="39"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -2196,7 +2220,7 @@
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="33"/>
+      <c r="D53" s="39"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -2221,7 +2245,7 @@
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="33"/>
+      <c r="D54" s="39"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -2246,7 +2270,7 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="33"/>
+      <c r="D55" s="39"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -2271,7 +2295,7 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="33"/>
+      <c r="D56" s="39"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
@@ -2296,7 +2320,7 @@
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="33"/>
+      <c r="D57" s="39"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -2321,7 +2345,7 @@
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="33"/>
+      <c r="D58" s="39"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
@@ -2346,7 +2370,7 @@
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="33"/>
+      <c r="D59" s="39"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
@@ -2371,7 +2395,7 @@
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="33"/>
+      <c r="D60" s="39"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
@@ -2396,7 +2420,7 @@
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="33"/>
+      <c r="D61" s="39"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
@@ -2421,7 +2445,7 @@
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="33"/>
+      <c r="D62" s="39"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
@@ -2446,7 +2470,7 @@
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="33"/>
+      <c r="D63" s="39"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
@@ -2471,7 +2495,7 @@
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="33"/>
+      <c r="D64" s="39"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
@@ -2496,7 +2520,7 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="33"/>
+      <c r="D65" s="39"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
@@ -2521,7 +2545,7 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="33"/>
+      <c r="D66" s="39"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -2546,7 +2570,7 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="33"/>
+      <c r="D67" s="39"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -2571,7 +2595,7 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="33"/>
+      <c r="D68" s="39"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -2596,7 +2620,7 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="33"/>
+      <c r="D69" s="39"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -2621,7 +2645,7 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="33"/>
+      <c r="D70" s="39"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -2646,7 +2670,7 @@
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="33"/>
+      <c r="D71" s="39"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -2671,7 +2695,7 @@
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="33"/>
+      <c r="D72" s="39"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -2696,7 +2720,7 @@
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="33"/>
+      <c r="D73" s="39"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
@@ -2721,7 +2745,7 @@
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="33"/>
+      <c r="D74" s="39"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
@@ -2746,7 +2770,7 @@
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="33"/>
+      <c r="D75" s="39"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
@@ -2771,7 +2795,7 @@
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="33"/>
+      <c r="D76" s="39"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
@@ -2796,7 +2820,7 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="33"/>
+      <c r="D77" s="39"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
@@ -2821,7 +2845,7 @@
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="33"/>
+      <c r="D78" s="39"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -2846,7 +2870,7 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="33"/>
+      <c r="D79" s="39"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -2871,7 +2895,7 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="33"/>
+      <c r="D80" s="39"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -2896,7 +2920,7 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="33"/>
+      <c r="D81" s="39"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -2921,7 +2945,7 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="33"/>
+      <c r="D82" s="39"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -2946,7 +2970,7 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="33"/>
+      <c r="D83" s="39"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -2971,7 +2995,7 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="33"/>
+      <c r="D84" s="39"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -2996,7 +3020,7 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="33"/>
+      <c r="D85" s="39"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
@@ -3021,7 +3045,7 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="33"/>
+      <c r="D86" s="39"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
@@ -3046,7 +3070,7 @@
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="33"/>
+      <c r="D87" s="39"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -3071,7 +3095,7 @@
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
-      <c r="D88" s="33"/>
+      <c r="D88" s="39"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
@@ -3096,7 +3120,7 @@
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
-      <c r="D89" s="33"/>
+      <c r="D89" s="39"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
@@ -3121,7 +3145,7 @@
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
-      <c r="D90" s="33"/>
+      <c r="D90" s="39"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
@@ -3146,7 +3170,7 @@
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
-      <c r="D91" s="33"/>
+      <c r="D91" s="39"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
@@ -3171,7 +3195,7 @@
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
-      <c r="D92" s="33"/>
+      <c r="D92" s="39"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
@@ -3196,7 +3220,7 @@
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
-      <c r="D93" s="33"/>
+      <c r="D93" s="39"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
@@ -3221,7 +3245,7 @@
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
-      <c r="D94" s="33"/>
+      <c r="D94" s="39"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
@@ -3246,7 +3270,7 @@
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
-      <c r="D95" s="33"/>
+      <c r="D95" s="39"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -3271,7 +3295,7 @@
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
-      <c r="D96" s="33"/>
+      <c r="D96" s="39"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -3296,7 +3320,7 @@
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
-      <c r="D97" s="33"/>
+      <c r="D97" s="39"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -3321,7 +3345,7 @@
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
-      <c r="D98" s="33"/>
+      <c r="D98" s="39"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -3346,7 +3370,7 @@
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
-      <c r="D99" s="33"/>
+      <c r="D99" s="39"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -3371,7 +3395,7 @@
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
-      <c r="D100" s="33"/>
+      <c r="D100" s="39"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -3396,7 +3420,7 @@
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
-      <c r="D101" s="33"/>
+      <c r="D101" s="39"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -3421,7 +3445,7 @@
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
-      <c r="D102" s="33"/>
+      <c r="D102" s="39"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
@@ -3446,7 +3470,7 @@
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
-      <c r="D103" s="33"/>
+      <c r="D103" s="39"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
@@ -3471,7 +3495,7 @@
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
-      <c r="D104" s="33"/>
+      <c r="D104" s="39"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
@@ -3496,7 +3520,7 @@
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
-      <c r="D105" s="33"/>
+      <c r="D105" s="39"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
@@ -3521,7 +3545,7 @@
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
-      <c r="D106" s="33"/>
+      <c r="D106" s="39"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
@@ -3546,7 +3570,7 @@
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
-      <c r="D107" s="33"/>
+      <c r="D107" s="39"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
@@ -3571,7 +3595,7 @@
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
-      <c r="D108" s="33"/>
+      <c r="D108" s="39"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
@@ -3596,7 +3620,7 @@
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
-      <c r="D109" s="33"/>
+      <c r="D109" s="39"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
@@ -3621,7 +3645,7 @@
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="33"/>
+      <c r="D110" s="39"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
@@ -3646,7 +3670,7 @@
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
-      <c r="D111" s="33"/>
+      <c r="D111" s="39"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
@@ -3671,7 +3695,7 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
-      <c r="D112" s="33"/>
+      <c r="D112" s="39"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
@@ -3696,7 +3720,7 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="33"/>
+      <c r="D113" s="39"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
@@ -3721,7 +3745,7 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="33"/>
+      <c r="D114" s="39"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
@@ -3746,7 +3770,7 @@
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="33"/>
+      <c r="D115" s="39"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
@@ -3771,7 +3795,7 @@
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="33"/>
+      <c r="D116" s="39"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
@@ -3796,7 +3820,7 @@
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="33"/>
+      <c r="D117" s="39"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
@@ -3821,7 +3845,7 @@
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="33"/>
+      <c r="D118" s="39"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
@@ -3846,7 +3870,7 @@
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
-      <c r="D119" s="33"/>
+      <c r="D119" s="39"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
@@ -3871,7 +3895,7 @@
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="33"/>
+      <c r="D120" s="39"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
@@ -3896,7 +3920,7 @@
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="33"/>
+      <c r="D121" s="39"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
@@ -3921,7 +3945,7 @@
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
-      <c r="D122" s="33"/>
+      <c r="D122" s="39"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
@@ -3946,7 +3970,7 @@
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="33"/>
+      <c r="D123" s="39"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
@@ -3971,7 +3995,7 @@
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
-      <c r="D124" s="33"/>
+      <c r="D124" s="39"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
@@ -3996,7 +4020,7 @@
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="33"/>
+      <c r="D125" s="39"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
@@ -4021,7 +4045,7 @@
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
-      <c r="D126" s="33"/>
+      <c r="D126" s="39"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
@@ -4046,7 +4070,7 @@
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
-      <c r="D127" s="33"/>
+      <c r="D127" s="39"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
@@ -4071,7 +4095,7 @@
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="33"/>
+      <c r="D128" s="39"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
@@ -4096,7 +4120,7 @@
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
-      <c r="D129" s="33"/>
+      <c r="D129" s="39"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
@@ -4121,7 +4145,7 @@
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
-      <c r="D130" s="33"/>
+      <c r="D130" s="39"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
@@ -4146,7 +4170,7 @@
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
-      <c r="D131" s="33"/>
+      <c r="D131" s="39"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
@@ -4171,7 +4195,7 @@
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
-      <c r="D132" s="33"/>
+      <c r="D132" s="39"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
@@ -4196,7 +4220,7 @@
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
-      <c r="D133" s="33"/>
+      <c r="D133" s="39"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
@@ -4221,7 +4245,7 @@
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
-      <c r="D134" s="33"/>
+      <c r="D134" s="39"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
@@ -4246,7 +4270,7 @@
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
-      <c r="D135" s="33"/>
+      <c r="D135" s="39"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
@@ -4271,7 +4295,7 @@
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
-      <c r="D136" s="33"/>
+      <c r="D136" s="39"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
@@ -4296,7 +4320,7 @@
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
-      <c r="D137" s="33"/>
+      <c r="D137" s="39"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
@@ -4321,7 +4345,7 @@
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
-      <c r="D138" s="33"/>
+      <c r="D138" s="39"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
@@ -4346,7 +4370,7 @@
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
-      <c r="D139" s="33"/>
+      <c r="D139" s="39"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
@@ -4371,7 +4395,7 @@
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
-      <c r="D140" s="33"/>
+      <c r="D140" s="39"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
@@ -4396,7 +4420,7 @@
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
-      <c r="D141" s="33"/>
+      <c r="D141" s="39"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
@@ -4421,7 +4445,7 @@
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
-      <c r="D142" s="33"/>
+      <c r="D142" s="39"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
@@ -4446,7 +4470,7 @@
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
-      <c r="D143" s="33"/>
+      <c r="D143" s="39"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
@@ -4471,7 +4495,7 @@
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
-      <c r="D144" s="33"/>
+      <c r="D144" s="39"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
@@ -4496,7 +4520,7 @@
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
-      <c r="D145" s="33"/>
+      <c r="D145" s="39"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3"/>
@@ -4521,7 +4545,7 @@
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
-      <c r="D146" s="33"/>
+      <c r="D146" s="39"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
@@ -4546,7 +4570,7 @@
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
-      <c r="D147" s="33"/>
+      <c r="D147" s="39"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
@@ -4571,7 +4595,7 @@
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
-      <c r="D148" s="33"/>
+      <c r="D148" s="39"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
@@ -4596,7 +4620,7 @@
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
-      <c r="D149" s="33"/>
+      <c r="D149" s="39"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3"/>
@@ -4621,7 +4645,7 @@
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
-      <c r="D150" s="33"/>
+      <c r="D150" s="39"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
@@ -4646,7 +4670,7 @@
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
-      <c r="D151" s="33"/>
+      <c r="D151" s="39"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>
@@ -4671,7 +4695,7 @@
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
-      <c r="D152" s="33"/>
+      <c r="D152" s="39"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
@@ -4696,7 +4720,7 @@
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
-      <c r="D153" s="33"/>
+      <c r="D153" s="39"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
@@ -4721,7 +4745,7 @@
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
-      <c r="D154" s="33"/>
+      <c r="D154" s="39"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
@@ -4746,7 +4770,7 @@
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
-      <c r="D155" s="33"/>
+      <c r="D155" s="39"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
@@ -4771,7 +4795,7 @@
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
-      <c r="D156" s="33"/>
+      <c r="D156" s="39"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
@@ -4796,7 +4820,7 @@
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
-      <c r="D157" s="33"/>
+      <c r="D157" s="39"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
@@ -4821,7 +4845,7 @@
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
-      <c r="D158" s="33"/>
+      <c r="D158" s="39"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
@@ -4846,7 +4870,7 @@
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
-      <c r="D159" s="33"/>
+      <c r="D159" s="39"/>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
@@ -4871,7 +4895,7 @@
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
-      <c r="D160" s="33"/>
+      <c r="D160" s="39"/>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
@@ -4896,7 +4920,7 @@
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
-      <c r="D161" s="33"/>
+      <c r="D161" s="39"/>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
@@ -4921,7 +4945,7 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
-      <c r="D162" s="33"/>
+      <c r="D162" s="39"/>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
@@ -4946,7 +4970,7 @@
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
-      <c r="D163" s="33"/>
+      <c r="D163" s="39"/>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
@@ -4971,7 +4995,7 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
-      <c r="D164" s="33"/>
+      <c r="D164" s="39"/>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
@@ -4996,7 +5020,7 @@
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
-      <c r="D165" s="33"/>
+      <c r="D165" s="39"/>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
@@ -5021,7 +5045,7 @@
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
-      <c r="D166" s="33"/>
+      <c r="D166" s="39"/>
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
@@ -5046,7 +5070,7 @@
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
-      <c r="D167" s="33"/>
+      <c r="D167" s="39"/>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
@@ -5071,7 +5095,7 @@
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
-      <c r="D168" s="33"/>
+      <c r="D168" s="39"/>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
@@ -5096,7 +5120,7 @@
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
-      <c r="D169" s="33"/>
+      <c r="D169" s="39"/>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
@@ -5121,7 +5145,7 @@
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
-      <c r="D170" s="33"/>
+      <c r="D170" s="39"/>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
@@ -5146,7 +5170,7 @@
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
-      <c r="D171" s="33"/>
+      <c r="D171" s="39"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
@@ -5171,7 +5195,7 @@
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
-      <c r="D172" s="33"/>
+      <c r="D172" s="39"/>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
@@ -5196,7 +5220,7 @@
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
-      <c r="D173" s="33"/>
+      <c r="D173" s="39"/>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3"/>
@@ -5221,7 +5245,7 @@
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
-      <c r="D174" s="33"/>
+      <c r="D174" s="39"/>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
@@ -5246,7 +5270,7 @@
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
-      <c r="D175" s="33"/>
+      <c r="D175" s="39"/>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
@@ -5271,7 +5295,7 @@
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="33"/>
+      <c r="D176" s="39"/>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="3"/>
@@ -5296,7 +5320,7 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
-      <c r="D177" s="33"/>
+      <c r="D177" s="39"/>
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="3"/>
@@ -5321,7 +5345,7 @@
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
-      <c r="D178" s="33"/>
+      <c r="D178" s="39"/>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="3"/>
@@ -5346,7 +5370,7 @@
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
-      <c r="D179" s="33"/>
+      <c r="D179" s="39"/>
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>
@@ -5371,7 +5395,7 @@
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
-      <c r="D180" s="33"/>
+      <c r="D180" s="39"/>
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3"/>
@@ -5396,7 +5420,7 @@
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
-      <c r="D181" s="33"/>
+      <c r="D181" s="39"/>
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="3"/>
@@ -5421,7 +5445,7 @@
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
-      <c r="D182" s="33"/>
+      <c r="D182" s="39"/>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="3"/>
@@ -5446,7 +5470,7 @@
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
-      <c r="D183" s="33"/>
+      <c r="D183" s="39"/>
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="3"/>
@@ -5471,7 +5495,7 @@
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
-      <c r="D184" s="33"/>
+      <c r="D184" s="39"/>
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="3"/>
@@ -5496,7 +5520,7 @@
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
-      <c r="D185" s="33"/>
+      <c r="D185" s="39"/>
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="G185" s="3"/>
@@ -5521,7 +5545,7 @@
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
-      <c r="D186" s="33"/>
+      <c r="D186" s="39"/>
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="G186" s="3"/>
@@ -5546,7 +5570,7 @@
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
-      <c r="D187" s="33"/>
+      <c r="D187" s="39"/>
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3"/>
@@ -5571,7 +5595,7 @@
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
-      <c r="D188" s="33"/>
+      <c r="D188" s="39"/>
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="G188" s="3"/>
@@ -5596,7 +5620,7 @@
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
-      <c r="D189" s="33"/>
+      <c r="D189" s="39"/>
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="3"/>
@@ -5621,7 +5645,7 @@
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
-      <c r="D190" s="33"/>
+      <c r="D190" s="39"/>
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="3"/>
@@ -5646,7 +5670,7 @@
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
-      <c r="D191" s="33"/>
+      <c r="D191" s="39"/>
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="3"/>
@@ -5671,7 +5695,7 @@
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
-      <c r="D192" s="33"/>
+      <c r="D192" s="39"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="3"/>
@@ -5696,7 +5720,7 @@
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
-      <c r="D193" s="33"/>
+      <c r="D193" s="39"/>
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
       <c r="G193" s="3"/>
@@ -5721,7 +5745,7 @@
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
-      <c r="D194" s="33"/>
+      <c r="D194" s="39"/>
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
       <c r="G194" s="3"/>
@@ -5746,7 +5770,7 @@
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
-      <c r="D195" s="33"/>
+      <c r="D195" s="39"/>
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="3"/>
@@ -5771,7 +5795,7 @@
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
-      <c r="D196" s="33"/>
+      <c r="D196" s="39"/>
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
@@ -5796,7 +5820,7 @@
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
-      <c r="D197" s="33"/>
+      <c r="D197" s="39"/>
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
       <c r="G197" s="3"/>
@@ -5821,7 +5845,7 @@
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
-      <c r="D198" s="33"/>
+      <c r="D198" s="39"/>
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
       <c r="G198" s="3"/>
@@ -5846,7 +5870,7 @@
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
-      <c r="D199" s="33"/>
+      <c r="D199" s="39"/>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="3"/>
@@ -5871,7 +5895,7 @@
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
-      <c r="D200" s="33"/>
+      <c r="D200" s="39"/>
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="3"/>
@@ -5896,7 +5920,7 @@
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
-      <c r="D201" s="33"/>
+      <c r="D201" s="39"/>
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
       <c r="G201" s="3"/>
@@ -5921,7 +5945,7 @@
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
-      <c r="D202" s="33"/>
+      <c r="D202" s="39"/>
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
       <c r="G202" s="3"/>
@@ -5946,7 +5970,7 @@
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
-      <c r="D203" s="33"/>
+      <c r="D203" s="39"/>
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
@@ -5971,7 +5995,7 @@
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
-      <c r="D204" s="33"/>
+      <c r="D204" s="39"/>
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="3"/>
@@ -5996,7 +6020,7 @@
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
-      <c r="D205" s="33"/>
+      <c r="D205" s="39"/>
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
       <c r="G205" s="3"/>
@@ -6021,7 +6045,7 @@
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
-      <c r="D206" s="33"/>
+      <c r="D206" s="39"/>
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
       <c r="G206" s="3"/>
@@ -6046,7 +6070,7 @@
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
-      <c r="D207" s="33"/>
+      <c r="D207" s="39"/>
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
       <c r="G207" s="3"/>
@@ -6071,7 +6095,7 @@
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
-      <c r="D208" s="33"/>
+      <c r="D208" s="39"/>
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
       <c r="G208" s="3"/>
@@ -6096,7 +6120,7 @@
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
-      <c r="D209" s="33"/>
+      <c r="D209" s="39"/>
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
       <c r="G209" s="3"/>
@@ -6121,7 +6145,7 @@
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
-      <c r="D210" s="33"/>
+      <c r="D210" s="39"/>
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
@@ -6146,7 +6170,7 @@
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
-      <c r="D211" s="33"/>
+      <c r="D211" s="39"/>
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
       <c r="G211" s="3"/>
@@ -6171,7 +6195,7 @@
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
-      <c r="D212" s="33"/>
+      <c r="D212" s="39"/>
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
       <c r="G212" s="3"/>
@@ -6196,7 +6220,7 @@
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
-      <c r="D213" s="33"/>
+      <c r="D213" s="39"/>
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
       <c r="G213" s="3"/>
@@ -6221,7 +6245,7 @@
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
-      <c r="D214" s="33"/>
+      <c r="D214" s="39"/>
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
       <c r="G214" s="3"/>
@@ -6246,7 +6270,7 @@
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
-      <c r="D215" s="33"/>
+      <c r="D215" s="39"/>
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
       <c r="G215" s="3"/>
@@ -6271,7 +6295,7 @@
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
-      <c r="D216" s="33"/>
+      <c r="D216" s="39"/>
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3"/>
@@ -6296,7 +6320,7 @@
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
-      <c r="D217" s="33"/>
+      <c r="D217" s="39"/>
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
       <c r="G217" s="3"/>
@@ -6321,7 +6345,7 @@
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
-      <c r="D218" s="33"/>
+      <c r="D218" s="39"/>
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
       <c r="G218" s="3"/>
@@ -6346,7 +6370,7 @@
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
-      <c r="D219" s="33"/>
+      <c r="D219" s="39"/>
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
@@ -6371,7 +6395,7 @@
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
-      <c r="D220" s="33"/>
+      <c r="D220" s="39"/>
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="G220" s="3"/>
@@ -6396,7 +6420,7 @@
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
-      <c r="D221" s="33"/>
+      <c r="D221" s="39"/>
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
       <c r="G221" s="3"/>
@@ -6421,7 +6445,7 @@
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
-      <c r="D222" s="33"/>
+      <c r="D222" s="39"/>
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
       <c r="G222" s="3"/>
@@ -6446,7 +6470,7 @@
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
-      <c r="D223" s="33"/>
+      <c r="D223" s="39"/>
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="3"/>
@@ -6471,7 +6495,7 @@
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
-      <c r="D224" s="33"/>
+      <c r="D224" s="39"/>
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
       <c r="G224" s="3"/>
@@ -6496,7 +6520,7 @@
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
-      <c r="D225" s="33"/>
+      <c r="D225" s="39"/>
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
       <c r="G225" s="3"/>
@@ -6521,7 +6545,7 @@
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
-      <c r="D226" s="33"/>
+      <c r="D226" s="39"/>
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
       <c r="G226" s="3"/>
@@ -6546,7 +6570,7 @@
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
-      <c r="D227" s="33"/>
+      <c r="D227" s="39"/>
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
       <c r="G227" s="3"/>
@@ -6571,7 +6595,7 @@
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
-      <c r="D228" s="33"/>
+      <c r="D228" s="39"/>
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
@@ -6596,7 +6620,7 @@
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
-      <c r="D229" s="33"/>
+      <c r="D229" s="39"/>
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
       <c r="G229" s="3"/>
@@ -6621,7 +6645,7 @@
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
-      <c r="D230" s="33"/>
+      <c r="D230" s="39"/>
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
       <c r="G230" s="3"/>
@@ -6646,7 +6670,7 @@
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
-      <c r="D231" s="33"/>
+      <c r="D231" s="39"/>
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
       <c r="G231" s="3"/>
@@ -6671,7 +6695,7 @@
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
-      <c r="D232" s="33"/>
+      <c r="D232" s="39"/>
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
       <c r="G232" s="3"/>
@@ -6696,7 +6720,7 @@
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
-      <c r="D233" s="33"/>
+      <c r="D233" s="39"/>
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
       <c r="G233" s="3"/>
@@ -6721,7 +6745,7 @@
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
-      <c r="D234" s="33"/>
+      <c r="D234" s="39"/>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
       <c r="G234" s="3"/>
@@ -6746,7 +6770,7 @@
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
-      <c r="D235" s="33"/>
+      <c r="D235" s="39"/>
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
       <c r="G235" s="3"/>
@@ -6771,7 +6795,7 @@
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
-      <c r="D236" s="33"/>
+      <c r="D236" s="39"/>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
       <c r="G236" s="3"/>
@@ -6796,7 +6820,7 @@
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
-      <c r="D237" s="33"/>
+      <c r="D237" s="39"/>
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
       <c r="G237" s="3"/>
@@ -6821,7 +6845,7 @@
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
-      <c r="D238" s="33"/>
+      <c r="D238" s="39"/>
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
       <c r="G238" s="3"/>
@@ -6846,7 +6870,7 @@
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
-      <c r="D239" s="33"/>
+      <c r="D239" s="39"/>
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
       <c r="G239" s="3"/>
@@ -6871,7 +6895,7 @@
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
-      <c r="D240" s="33"/>
+      <c r="D240" s="39"/>
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
@@ -6896,7 +6920,7 @@
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
-      <c r="D241" s="33"/>
+      <c r="D241" s="39"/>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
@@ -6921,7 +6945,7 @@
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
-      <c r="D242" s="33"/>
+      <c r="D242" s="39"/>
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
@@ -6946,7 +6970,7 @@
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
-      <c r="D243" s="33"/>
+      <c r="D243" s="39"/>
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
       <c r="G243" s="3"/>
@@ -6971,7 +6995,7 @@
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
-      <c r="D244" s="33"/>
+      <c r="D244" s="39"/>
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
       <c r="G244" s="3"/>
@@ -6996,7 +7020,7 @@
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
-      <c r="D245" s="33"/>
+      <c r="D245" s="39"/>
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3"/>
@@ -7021,7 +7045,7 @@
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
-      <c r="D246" s="33"/>
+      <c r="D246" s="39"/>
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
       <c r="G246" s="3"/>
@@ -7046,7 +7070,7 @@
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
-      <c r="D247" s="33"/>
+      <c r="D247" s="39"/>
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
       <c r="G247" s="3"/>
@@ -7071,7 +7095,7 @@
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
-      <c r="D248" s="33"/>
+      <c r="D248" s="39"/>
       <c r="E248" s="3"/>
       <c r="F248" s="3"/>
       <c r="G248" s="3"/>
@@ -7096,7 +7120,7 @@
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
-      <c r="D249" s="33"/>
+      <c r="D249" s="39"/>
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
       <c r="G249" s="3"/>
@@ -7121,7 +7145,7 @@
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
-      <c r="D250" s="33"/>
+      <c r="D250" s="39"/>
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
       <c r="G250" s="3"/>
@@ -7146,7 +7170,7 @@
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
-      <c r="D251" s="33"/>
+      <c r="D251" s="39"/>
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
       <c r="G251" s="3"/>
@@ -7171,7 +7195,7 @@
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
-      <c r="D252" s="33"/>
+      <c r="D252" s="39"/>
       <c r="E252" s="3"/>
       <c r="F252" s="3"/>
       <c r="G252" s="3"/>
@@ -7196,7 +7220,7 @@
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
-      <c r="D253" s="33"/>
+      <c r="D253" s="39"/>
       <c r="E253" s="3"/>
       <c r="F253" s="3"/>
       <c r="G253" s="3"/>
@@ -7221,7 +7245,7 @@
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
-      <c r="D254" s="33"/>
+      <c r="D254" s="39"/>
       <c r="E254" s="3"/>
       <c r="F254" s="3"/>
       <c r="G254" s="3"/>
@@ -7246,7 +7270,7 @@
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
-      <c r="D255" s="33"/>
+      <c r="D255" s="39"/>
       <c r="E255" s="3"/>
       <c r="F255" s="3"/>
       <c r="G255" s="3"/>
@@ -7271,7 +7295,7 @@
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
-      <c r="D256" s="33"/>
+      <c r="D256" s="39"/>
       <c r="E256" s="3"/>
       <c r="F256" s="3"/>
       <c r="G256" s="3"/>
@@ -7296,7 +7320,7 @@
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
-      <c r="D257" s="33"/>
+      <c r="D257" s="39"/>
       <c r="E257" s="3"/>
       <c r="F257" s="3"/>
       <c r="G257" s="3"/>
@@ -7321,7 +7345,7 @@
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
-      <c r="D258" s="33"/>
+      <c r="D258" s="39"/>
       <c r="E258" s="3"/>
       <c r="F258" s="3"/>
       <c r="G258" s="3"/>
@@ -7346,7 +7370,7 @@
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
-      <c r="D259" s="33"/>
+      <c r="D259" s="39"/>
       <c r="E259" s="3"/>
       <c r="F259" s="3"/>
       <c r="G259" s="3"/>
@@ -7371,7 +7395,7 @@
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
-      <c r="D260" s="33"/>
+      <c r="D260" s="39"/>
       <c r="E260" s="3"/>
       <c r="F260" s="3"/>
       <c r="G260" s="3"/>
@@ -7396,7 +7420,7 @@
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
-      <c r="D261" s="33"/>
+      <c r="D261" s="39"/>
       <c r="E261" s="3"/>
       <c r="F261" s="3"/>
       <c r="G261" s="3"/>
@@ -7421,7 +7445,7 @@
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
-      <c r="D262" s="33"/>
+      <c r="D262" s="39"/>
       <c r="E262" s="3"/>
       <c r="F262" s="3"/>
       <c r="G262" s="3"/>
@@ -7446,7 +7470,7 @@
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
-      <c r="D263" s="33"/>
+      <c r="D263" s="39"/>
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
       <c r="G263" s="3"/>
@@ -7471,7 +7495,7 @@
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
-      <c r="D264" s="33"/>
+      <c r="D264" s="39"/>
       <c r="E264" s="3"/>
       <c r="F264" s="3"/>
       <c r="G264" s="3"/>
@@ -7496,7 +7520,7 @@
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
-      <c r="D265" s="33"/>
+      <c r="D265" s="39"/>
       <c r="E265" s="3"/>
       <c r="F265" s="3"/>
       <c r="G265" s="3"/>
@@ -7521,7 +7545,7 @@
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
-      <c r="D266" s="33"/>
+      <c r="D266" s="39"/>
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
       <c r="G266" s="3"/>
@@ -7546,7 +7570,7 @@
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
-      <c r="D267" s="33"/>
+      <c r="D267" s="39"/>
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
       <c r="G267" s="3"/>
@@ -7571,7 +7595,7 @@
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
-      <c r="D268" s="33"/>
+      <c r="D268" s="39"/>
       <c r="E268" s="3"/>
       <c r="F268" s="3"/>
       <c r="G268" s="3"/>
@@ -7596,7 +7620,7 @@
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
-      <c r="D269" s="33"/>
+      <c r="D269" s="39"/>
       <c r="E269" s="3"/>
       <c r="F269" s="3"/>
       <c r="G269" s="3"/>
@@ -7621,7 +7645,7 @@
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
-      <c r="D270" s="33"/>
+      <c r="D270" s="39"/>
       <c r="E270" s="3"/>
       <c r="F270" s="3"/>
       <c r="G270" s="3"/>
@@ -7646,7 +7670,7 @@
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
-      <c r="D271" s="33"/>
+      <c r="D271" s="39"/>
       <c r="E271" s="3"/>
       <c r="F271" s="3"/>
       <c r="G271" s="3"/>
@@ -7671,7 +7695,7 @@
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
-      <c r="D272" s="33"/>
+      <c r="D272" s="39"/>
       <c r="E272" s="3"/>
       <c r="F272" s="3"/>
       <c r="G272" s="3"/>
@@ -7696,7 +7720,7 @@
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
-      <c r="D273" s="33"/>
+      <c r="D273" s="39"/>
       <c r="E273" s="3"/>
       <c r="F273" s="3"/>
       <c r="G273" s="3"/>
@@ -7721,7 +7745,7 @@
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
-      <c r="D274" s="33"/>
+      <c r="D274" s="39"/>
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="G274" s="3"/>
@@ -7746,7 +7770,7 @@
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
-      <c r="D275" s="33"/>
+      <c r="D275" s="39"/>
       <c r="E275" s="3"/>
       <c r="F275" s="3"/>
       <c r="G275" s="3"/>
@@ -7771,7 +7795,7 @@
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
-      <c r="D276" s="33"/>
+      <c r="D276" s="39"/>
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
       <c r="G276" s="3"/>
@@ -7796,7 +7820,7 @@
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
-      <c r="D277" s="33"/>
+      <c r="D277" s="39"/>
       <c r="E277" s="3"/>
       <c r="F277" s="3"/>
       <c r="G277" s="3"/>
@@ -7821,7 +7845,7 @@
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
-      <c r="D278" s="33"/>
+      <c r="D278" s="39"/>
       <c r="E278" s="3"/>
       <c r="F278" s="3"/>
       <c r="G278" s="3"/>
@@ -7846,7 +7870,7 @@
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
-      <c r="D279" s="33"/>
+      <c r="D279" s="39"/>
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
       <c r="G279" s="3"/>
@@ -7871,7 +7895,7 @@
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
-      <c r="D280" s="33"/>
+      <c r="D280" s="39"/>
       <c r="E280" s="3"/>
       <c r="F280" s="3"/>
       <c r="G280" s="3"/>
@@ -7896,7 +7920,7 @@
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
-      <c r="D281" s="33"/>
+      <c r="D281" s="39"/>
       <c r="E281" s="3"/>
       <c r="F281" s="3"/>
       <c r="G281" s="3"/>
@@ -7921,7 +7945,7 @@
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
-      <c r="D282" s="33"/>
+      <c r="D282" s="39"/>
       <c r="E282" s="3"/>
       <c r="F282" s="3"/>
       <c r="G282" s="3"/>
@@ -7946,7 +7970,7 @@
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
-      <c r="D283" s="33"/>
+      <c r="D283" s="39"/>
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
       <c r="G283" s="3"/>
@@ -7971,7 +7995,7 @@
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
-      <c r="D284" s="33"/>
+      <c r="D284" s="39"/>
       <c r="E284" s="3"/>
       <c r="F284" s="3"/>
       <c r="G284" s="3"/>
@@ -7996,7 +8020,7 @@
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
-      <c r="D285" s="33"/>
+      <c r="D285" s="39"/>
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
       <c r="G285" s="3"/>
@@ -8021,7 +8045,7 @@
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
-      <c r="D286" s="33"/>
+      <c r="D286" s="39"/>
       <c r="E286" s="3"/>
       <c r="F286" s="3"/>
       <c r="G286" s="3"/>
@@ -8046,7 +8070,7 @@
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
-      <c r="D287" s="33"/>
+      <c r="D287" s="39"/>
       <c r="E287" s="3"/>
       <c r="F287" s="3"/>
       <c r="G287" s="3"/>
@@ -8071,7 +8095,7 @@
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
-      <c r="D288" s="33"/>
+      <c r="D288" s="39"/>
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
       <c r="G288" s="3"/>
@@ -8096,7 +8120,7 @@
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
-      <c r="D289" s="33"/>
+      <c r="D289" s="39"/>
       <c r="E289" s="3"/>
       <c r="F289" s="3"/>
       <c r="G289" s="3"/>
@@ -8121,7 +8145,7 @@
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
-      <c r="D290" s="33"/>
+      <c r="D290" s="39"/>
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
       <c r="G290" s="3"/>
@@ -8146,7 +8170,7 @@
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
-      <c r="D291" s="33"/>
+      <c r="D291" s="39"/>
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
       <c r="G291" s="3"/>
@@ -8171,7 +8195,7 @@
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
-      <c r="D292" s="33"/>
+      <c r="D292" s="39"/>
       <c r="E292" s="3"/>
       <c r="F292" s="3"/>
       <c r="G292" s="3"/>
@@ -8196,7 +8220,7 @@
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
-      <c r="D293" s="33"/>
+      <c r="D293" s="39"/>
       <c r="E293" s="3"/>
       <c r="F293" s="3"/>
       <c r="G293" s="3"/>
@@ -8221,7 +8245,7 @@
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
-      <c r="D294" s="33"/>
+      <c r="D294" s="39"/>
       <c r="E294" s="3"/>
       <c r="F294" s="3"/>
       <c r="G294" s="3"/>
@@ -8246,7 +8270,7 @@
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
-      <c r="D295" s="33"/>
+      <c r="D295" s="39"/>
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
       <c r="G295" s="3"/>
@@ -8271,7 +8295,7 @@
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
-      <c r="D296" s="33"/>
+      <c r="D296" s="39"/>
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
       <c r="G296" s="3"/>
@@ -8296,7 +8320,7 @@
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
-      <c r="D297" s="33"/>
+      <c r="D297" s="39"/>
       <c r="E297" s="3"/>
       <c r="F297" s="3"/>
       <c r="G297" s="3"/>
@@ -8321,7 +8345,7 @@
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
-      <c r="D298" s="33"/>
+      <c r="D298" s="39"/>
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
       <c r="G298" s="3"/>
@@ -8346,7 +8370,7 @@
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
-      <c r="D299" s="33"/>
+      <c r="D299" s="39"/>
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
       <c r="G299" s="3"/>
@@ -8371,7 +8395,7 @@
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
-      <c r="D300" s="33"/>
+      <c r="D300" s="39"/>
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
       <c r="G300" s="3"/>
@@ -8396,7 +8420,7 @@
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
-      <c r="D301" s="33"/>
+      <c r="D301" s="39"/>
       <c r="E301" s="3"/>
       <c r="F301" s="3"/>
       <c r="G301" s="3"/>
@@ -8421,7 +8445,7 @@
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
-      <c r="D302" s="33"/>
+      <c r="D302" s="39"/>
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
       <c r="G302" s="3"/>
@@ -8446,7 +8470,7 @@
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
-      <c r="D303" s="33"/>
+      <c r="D303" s="39"/>
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="G303" s="3"/>
@@ -8471,7 +8495,7 @@
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
-      <c r="D304" s="33"/>
+      <c r="D304" s="39"/>
       <c r="E304" s="3"/>
       <c r="F304" s="3"/>
       <c r="G304" s="3"/>
@@ -8496,7 +8520,7 @@
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
-      <c r="D305" s="33"/>
+      <c r="D305" s="39"/>
       <c r="E305" s="3"/>
       <c r="F305" s="3"/>
       <c r="G305" s="3"/>
@@ -8521,7 +8545,7 @@
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
-      <c r="D306" s="33"/>
+      <c r="D306" s="39"/>
       <c r="E306" s="3"/>
       <c r="F306" s="3"/>
       <c r="G306" s="3"/>
@@ -8546,7 +8570,7 @@
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
-      <c r="D307" s="33"/>
+      <c r="D307" s="39"/>
       <c r="E307" s="3"/>
       <c r="F307" s="3"/>
       <c r="G307" s="3"/>
@@ -8571,7 +8595,7 @@
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
-      <c r="D308" s="33"/>
+      <c r="D308" s="39"/>
       <c r="E308" s="3"/>
       <c r="F308" s="3"/>
       <c r="G308" s="3"/>
@@ -8596,7 +8620,7 @@
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
-      <c r="D309" s="33"/>
+      <c r="D309" s="39"/>
       <c r="E309" s="3"/>
       <c r="F309" s="3"/>
       <c r="G309" s="3"/>
@@ -8621,7 +8645,7 @@
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
-      <c r="D310" s="33"/>
+      <c r="D310" s="39"/>
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
       <c r="G310" s="3"/>
@@ -8646,7 +8670,7 @@
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
-      <c r="D311" s="33"/>
+      <c r="D311" s="39"/>
       <c r="E311" s="3"/>
       <c r="F311" s="3"/>
       <c r="G311" s="3"/>
@@ -8671,7 +8695,7 @@
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
-      <c r="D312" s="33"/>
+      <c r="D312" s="39"/>
       <c r="E312" s="3"/>
       <c r="F312" s="3"/>
       <c r="G312" s="3"/>
@@ -8696,7 +8720,7 @@
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
-      <c r="D313" s="33"/>
+      <c r="D313" s="39"/>
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
       <c r="G313" s="3"/>
@@ -8721,7 +8745,7 @@
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
-      <c r="D314" s="33"/>
+      <c r="D314" s="39"/>
       <c r="E314" s="3"/>
       <c r="F314" s="3"/>
       <c r="G314" s="3"/>
@@ -8746,7 +8770,7 @@
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
-      <c r="D315" s="33"/>
+      <c r="D315" s="39"/>
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
       <c r="G315" s="3"/>
@@ -8771,7 +8795,7 @@
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
-      <c r="D316" s="33"/>
+      <c r="D316" s="39"/>
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
       <c r="G316" s="3"/>
@@ -8796,7 +8820,7 @@
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
-      <c r="D317" s="33"/>
+      <c r="D317" s="39"/>
       <c r="E317" s="3"/>
       <c r="F317" s="3"/>
       <c r="G317" s="3"/>
@@ -8821,7 +8845,7 @@
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
-      <c r="D318" s="33"/>
+      <c r="D318" s="39"/>
       <c r="E318" s="3"/>
       <c r="F318" s="3"/>
       <c r="G318" s="3"/>
@@ -8846,7 +8870,7 @@
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
-      <c r="D319" s="33"/>
+      <c r="D319" s="39"/>
       <c r="E319" s="3"/>
       <c r="F319" s="3"/>
       <c r="G319" s="3"/>
@@ -8871,7 +8895,7 @@
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
-      <c r="D320" s="33"/>
+      <c r="D320" s="39"/>
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
       <c r="G320" s="3"/>
@@ -8896,7 +8920,7 @@
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
-      <c r="D321" s="33"/>
+      <c r="D321" s="39"/>
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
       <c r="G321" s="3"/>
@@ -8921,7 +8945,7 @@
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
-      <c r="D322" s="33"/>
+      <c r="D322" s="39"/>
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
       <c r="G322" s="3"/>
@@ -8946,7 +8970,7 @@
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
-      <c r="D323" s="33"/>
+      <c r="D323" s="39"/>
       <c r="E323" s="3"/>
       <c r="F323" s="3"/>
       <c r="G323" s="3"/>
@@ -8971,7 +8995,7 @@
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
-      <c r="D324" s="33"/>
+      <c r="D324" s="39"/>
       <c r="E324" s="3"/>
       <c r="F324" s="3"/>
       <c r="G324" s="3"/>
@@ -8996,7 +9020,7 @@
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
-      <c r="D325" s="33"/>
+      <c r="D325" s="39"/>
       <c r="E325" s="3"/>
       <c r="F325" s="3"/>
       <c r="G325" s="3"/>
@@ -9021,7 +9045,7 @@
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
-      <c r="D326" s="33"/>
+      <c r="D326" s="39"/>
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
       <c r="G326" s="3"/>
@@ -9046,7 +9070,7 @@
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
-      <c r="D327" s="33"/>
+      <c r="D327" s="39"/>
       <c r="E327" s="3"/>
       <c r="F327" s="3"/>
       <c r="G327" s="3"/>
@@ -9071,7 +9095,7 @@
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
-      <c r="D328" s="33"/>
+      <c r="D328" s="39"/>
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
       <c r="G328" s="3"/>
@@ -9096,7 +9120,7 @@
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
-      <c r="D329" s="33"/>
+      <c r="D329" s="39"/>
       <c r="E329" s="3"/>
       <c r="F329" s="3"/>
       <c r="G329" s="3"/>
@@ -9121,7 +9145,7 @@
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
-      <c r="D330" s="33"/>
+      <c r="D330" s="39"/>
       <c r="E330" s="3"/>
       <c r="F330" s="3"/>
       <c r="G330" s="3"/>
@@ -9146,7 +9170,7 @@
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
-      <c r="D331" s="33"/>
+      <c r="D331" s="39"/>
       <c r="E331" s="3"/>
       <c r="F331" s="3"/>
       <c r="G331" s="3"/>
@@ -9171,7 +9195,7 @@
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
-      <c r="D332" s="33"/>
+      <c r="D332" s="39"/>
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="G332" s="3"/>
@@ -9196,7 +9220,7 @@
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
-      <c r="D333" s="33"/>
+      <c r="D333" s="39"/>
       <c r="E333" s="3"/>
       <c r="F333" s="3"/>
       <c r="G333" s="3"/>
@@ -9221,7 +9245,7 @@
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
-      <c r="D334" s="33"/>
+      <c r="D334" s="39"/>
       <c r="E334" s="3"/>
       <c r="F334" s="3"/>
       <c r="G334" s="3"/>
@@ -9246,7 +9270,7 @@
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
-      <c r="D335" s="33"/>
+      <c r="D335" s="39"/>
       <c r="E335" s="3"/>
       <c r="F335" s="3"/>
       <c r="G335" s="3"/>
@@ -9271,7 +9295,7 @@
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
-      <c r="D336" s="33"/>
+      <c r="D336" s="39"/>
       <c r="E336" s="3"/>
       <c r="F336" s="3"/>
       <c r="G336" s="3"/>
@@ -9296,7 +9320,7 @@
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
-      <c r="D337" s="33"/>
+      <c r="D337" s="39"/>
       <c r="E337" s="3"/>
       <c r="F337" s="3"/>
       <c r="G337" s="3"/>
@@ -9321,7 +9345,7 @@
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
-      <c r="D338" s="33"/>
+      <c r="D338" s="39"/>
       <c r="E338" s="3"/>
       <c r="F338" s="3"/>
       <c r="G338" s="3"/>
@@ -9346,7 +9370,7 @@
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
-      <c r="D339" s="33"/>
+      <c r="D339" s="39"/>
       <c r="E339" s="3"/>
       <c r="F339" s="3"/>
       <c r="G339" s="3"/>
@@ -9371,7 +9395,7 @@
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
-      <c r="D340" s="33"/>
+      <c r="D340" s="39"/>
       <c r="E340" s="3"/>
       <c r="F340" s="3"/>
       <c r="G340" s="3"/>
@@ -9396,7 +9420,7 @@
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
-      <c r="D341" s="33"/>
+      <c r="D341" s="39"/>
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
       <c r="G341" s="3"/>
@@ -9421,7 +9445,7 @@
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
-      <c r="D342" s="33"/>
+      <c r="D342" s="39"/>
       <c r="E342" s="3"/>
       <c r="F342" s="3"/>
       <c r="G342" s="3"/>
@@ -9446,7 +9470,7 @@
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
-      <c r="D343" s="33"/>
+      <c r="D343" s="39"/>
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
       <c r="G343" s="3"/>
@@ -9471,7 +9495,7 @@
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
-      <c r="D344" s="33"/>
+      <c r="D344" s="39"/>
       <c r="E344" s="3"/>
       <c r="F344" s="3"/>
       <c r="G344" s="3"/>
@@ -9496,7 +9520,7 @@
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
-      <c r="D345" s="33"/>
+      <c r="D345" s="39"/>
       <c r="E345" s="3"/>
       <c r="F345" s="3"/>
       <c r="G345" s="3"/>
@@ -9521,7 +9545,7 @@
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
-      <c r="D346" s="33"/>
+      <c r="D346" s="39"/>
       <c r="E346" s="3"/>
       <c r="F346" s="3"/>
       <c r="G346" s="3"/>
@@ -9546,7 +9570,7 @@
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
-      <c r="D347" s="33"/>
+      <c r="D347" s="39"/>
       <c r="E347" s="3"/>
       <c r="F347" s="3"/>
       <c r="G347" s="3"/>
@@ -9571,7 +9595,7 @@
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
-      <c r="D348" s="33"/>
+      <c r="D348" s="39"/>
       <c r="E348" s="3"/>
       <c r="F348" s="3"/>
       <c r="G348" s="3"/>
@@ -9596,7 +9620,7 @@
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
-      <c r="D349" s="33"/>
+      <c r="D349" s="39"/>
       <c r="E349" s="3"/>
       <c r="F349" s="3"/>
       <c r="G349" s="3"/>
@@ -9621,7 +9645,7 @@
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
-      <c r="D350" s="33"/>
+      <c r="D350" s="39"/>
       <c r="E350" s="3"/>
       <c r="F350" s="3"/>
       <c r="G350" s="3"/>
@@ -9646,7 +9670,7 @@
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
-      <c r="D351" s="33"/>
+      <c r="D351" s="39"/>
       <c r="E351" s="3"/>
       <c r="F351" s="3"/>
       <c r="G351" s="3"/>
@@ -9671,7 +9695,7 @@
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
-      <c r="D352" s="33"/>
+      <c r="D352" s="39"/>
       <c r="E352" s="3"/>
       <c r="F352" s="3"/>
       <c r="G352" s="3"/>
@@ -9696,7 +9720,7 @@
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
-      <c r="D353" s="33"/>
+      <c r="D353" s="39"/>
       <c r="E353" s="3"/>
       <c r="F353" s="3"/>
       <c r="G353" s="3"/>
@@ -9721,7 +9745,7 @@
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
-      <c r="D354" s="33"/>
+      <c r="D354" s="39"/>
       <c r="E354" s="3"/>
       <c r="F354" s="3"/>
       <c r="G354" s="3"/>
@@ -9746,7 +9770,7 @@
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
-      <c r="D355" s="33"/>
+      <c r="D355" s="39"/>
       <c r="E355" s="3"/>
       <c r="F355" s="3"/>
       <c r="G355" s="3"/>
@@ -9771,7 +9795,7 @@
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
-      <c r="D356" s="33"/>
+      <c r="D356" s="39"/>
       <c r="E356" s="3"/>
       <c r="F356" s="3"/>
       <c r="G356" s="3"/>
@@ -9796,7 +9820,7 @@
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
-      <c r="D357" s="33"/>
+      <c r="D357" s="39"/>
       <c r="E357" s="3"/>
       <c r="F357" s="3"/>
       <c r="G357" s="3"/>
@@ -9821,7 +9845,7 @@
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
-      <c r="D358" s="33"/>
+      <c r="D358" s="39"/>
       <c r="E358" s="3"/>
       <c r="F358" s="3"/>
       <c r="G358" s="3"/>
@@ -9846,7 +9870,7 @@
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
-      <c r="D359" s="33"/>
+      <c r="D359" s="39"/>
       <c r="E359" s="3"/>
       <c r="F359" s="3"/>
       <c r="G359" s="3"/>
@@ -9871,7 +9895,7 @@
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
-      <c r="D360" s="33"/>
+      <c r="D360" s="39"/>
       <c r="E360" s="3"/>
       <c r="F360" s="3"/>
       <c r="G360" s="3"/>
@@ -9896,7 +9920,7 @@
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
-      <c r="D361" s="33"/>
+      <c r="D361" s="39"/>
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
       <c r="G361" s="3"/>
@@ -9921,7 +9945,7 @@
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
-      <c r="D362" s="33"/>
+      <c r="D362" s="39"/>
       <c r="E362" s="3"/>
       <c r="F362" s="3"/>
       <c r="G362" s="3"/>
@@ -9946,7 +9970,7 @@
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
-      <c r="D363" s="33"/>
+      <c r="D363" s="39"/>
       <c r="E363" s="3"/>
       <c r="F363" s="3"/>
       <c r="G363" s="3"/>
@@ -9971,7 +9995,7 @@
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
-      <c r="D364" s="33"/>
+      <c r="D364" s="39"/>
       <c r="E364" s="3"/>
       <c r="F364" s="3"/>
       <c r="G364" s="3"/>
@@ -9996,7 +10020,7 @@
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
-      <c r="D365" s="33"/>
+      <c r="D365" s="39"/>
       <c r="E365" s="3"/>
       <c r="F365" s="3"/>
       <c r="G365" s="3"/>
@@ -10021,7 +10045,7 @@
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
-      <c r="D366" s="33"/>
+      <c r="D366" s="39"/>
       <c r="E366" s="3"/>
       <c r="F366" s="3"/>
       <c r="G366" s="3"/>
@@ -10046,7 +10070,7 @@
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
-      <c r="D367" s="33"/>
+      <c r="D367" s="39"/>
       <c r="E367" s="3"/>
       <c r="F367" s="3"/>
       <c r="G367" s="3"/>
@@ -10071,7 +10095,7 @@
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
-      <c r="D368" s="33"/>
+      <c r="D368" s="39"/>
       <c r="E368" s="3"/>
       <c r="F368" s="3"/>
       <c r="G368" s="3"/>
@@ -10096,7 +10120,7 @@
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
-      <c r="D369" s="33"/>
+      <c r="D369" s="39"/>
       <c r="E369" s="3"/>
       <c r="F369" s="3"/>
       <c r="G369" s="3"/>
@@ -10121,7 +10145,7 @@
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
-      <c r="D370" s="33"/>
+      <c r="D370" s="39"/>
       <c r="E370" s="3"/>
       <c r="F370" s="3"/>
       <c r="G370" s="3"/>
@@ -10146,7 +10170,7 @@
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
-      <c r="D371" s="33"/>
+      <c r="D371" s="39"/>
       <c r="E371" s="3"/>
       <c r="F371" s="3"/>
       <c r="G371" s="3"/>
@@ -10171,7 +10195,7 @@
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
-      <c r="D372" s="33"/>
+      <c r="D372" s="39"/>
       <c r="E372" s="3"/>
       <c r="F372" s="3"/>
       <c r="G372" s="3"/>
@@ -10196,7 +10220,7 @@
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
-      <c r="D373" s="33"/>
+      <c r="D373" s="39"/>
       <c r="E373" s="3"/>
       <c r="F373" s="3"/>
       <c r="G373" s="3"/>
@@ -10221,7 +10245,7 @@
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
-      <c r="D374" s="33"/>
+      <c r="D374" s="39"/>
       <c r="E374" s="3"/>
       <c r="F374" s="3"/>
       <c r="G374" s="3"/>
@@ -10246,7 +10270,7 @@
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
-      <c r="D375" s="33"/>
+      <c r="D375" s="39"/>
       <c r="E375" s="3"/>
       <c r="F375" s="3"/>
       <c r="G375" s="3"/>
@@ -10271,7 +10295,7 @@
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
-      <c r="D376" s="33"/>
+      <c r="D376" s="39"/>
       <c r="E376" s="3"/>
       <c r="F376" s="3"/>
       <c r="G376" s="3"/>
@@ -10296,7 +10320,7 @@
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
-      <c r="D377" s="33"/>
+      <c r="D377" s="39"/>
       <c r="E377" s="3"/>
       <c r="F377" s="3"/>
       <c r="G377" s="3"/>
@@ -10321,7 +10345,7 @@
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
-      <c r="D378" s="33"/>
+      <c r="D378" s="39"/>
       <c r="E378" s="3"/>
       <c r="F378" s="3"/>
       <c r="G378" s="3"/>
@@ -10346,7 +10370,7 @@
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
-      <c r="D379" s="33"/>
+      <c r="D379" s="39"/>
       <c r="E379" s="3"/>
       <c r="F379" s="3"/>
       <c r="G379" s="3"/>
@@ -10371,7 +10395,7 @@
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
-      <c r="D380" s="33"/>
+      <c r="D380" s="39"/>
       <c r="E380" s="3"/>
       <c r="F380" s="3"/>
       <c r="G380" s="3"/>
@@ -10396,7 +10420,7 @@
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
-      <c r="D381" s="33"/>
+      <c r="D381" s="39"/>
       <c r="E381" s="3"/>
       <c r="F381" s="3"/>
       <c r="G381" s="3"/>
@@ -10421,7 +10445,7 @@
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
-      <c r="D382" s="33"/>
+      <c r="D382" s="39"/>
       <c r="E382" s="3"/>
       <c r="F382" s="3"/>
       <c r="G382" s="3"/>
@@ -10446,7 +10470,7 @@
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
-      <c r="D383" s="33"/>
+      <c r="D383" s="39"/>
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
       <c r="G383" s="3"/>
@@ -10471,7 +10495,7 @@
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
-      <c r="D384" s="33"/>
+      <c r="D384" s="39"/>
       <c r="E384" s="3"/>
       <c r="F384" s="3"/>
       <c r="G384" s="3"/>
@@ -10496,7 +10520,7 @@
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
-      <c r="D385" s="33"/>
+      <c r="D385" s="39"/>
       <c r="E385" s="3"/>
       <c r="F385" s="3"/>
       <c r="G385" s="3"/>
@@ -10521,7 +10545,7 @@
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
-      <c r="D386" s="33"/>
+      <c r="D386" s="39"/>
       <c r="E386" s="3"/>
       <c r="F386" s="3"/>
       <c r="G386" s="3"/>
@@ -10546,7 +10570,7 @@
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
-      <c r="D387" s="33"/>
+      <c r="D387" s="39"/>
       <c r="E387" s="3"/>
       <c r="F387" s="3"/>
       <c r="G387" s="3"/>
@@ -10571,7 +10595,7 @@
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
-      <c r="D388" s="33"/>
+      <c r="D388" s="39"/>
       <c r="E388" s="3"/>
       <c r="F388" s="3"/>
       <c r="G388" s="3"/>
@@ -10596,7 +10620,7 @@
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
-      <c r="D389" s="33"/>
+      <c r="D389" s="39"/>
       <c r="E389" s="3"/>
       <c r="F389" s="3"/>
       <c r="G389" s="3"/>
@@ -10621,7 +10645,7 @@
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
-      <c r="D390" s="33"/>
+      <c r="D390" s="39"/>
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
       <c r="G390" s="3"/>
@@ -10646,7 +10670,7 @@
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
-      <c r="D391" s="33"/>
+      <c r="D391" s="39"/>
       <c r="E391" s="3"/>
       <c r="F391" s="3"/>
       <c r="G391" s="3"/>
@@ -10671,7 +10695,7 @@
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
-      <c r="D392" s="33"/>
+      <c r="D392" s="39"/>
       <c r="E392" s="3"/>
       <c r="F392" s="3"/>
       <c r="G392" s="3"/>
@@ -10696,7 +10720,7 @@
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
-      <c r="D393" s="33"/>
+      <c r="D393" s="39"/>
       <c r="E393" s="3"/>
       <c r="F393" s="3"/>
       <c r="G393" s="3"/>
@@ -10721,7 +10745,7 @@
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
-      <c r="D394" s="33"/>
+      <c r="D394" s="39"/>
       <c r="E394" s="3"/>
       <c r="F394" s="3"/>
       <c r="G394" s="3"/>
@@ -10746,7 +10770,7 @@
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
-      <c r="D395" s="33"/>
+      <c r="D395" s="39"/>
       <c r="E395" s="3"/>
       <c r="F395" s="3"/>
       <c r="G395" s="3"/>
@@ -10771,7 +10795,7 @@
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
-      <c r="D396" s="33"/>
+      <c r="D396" s="39"/>
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
       <c r="G396" s="3"/>
@@ -10796,7 +10820,7 @@
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
-      <c r="D397" s="33"/>
+      <c r="D397" s="39"/>
       <c r="E397" s="3"/>
       <c r="F397" s="3"/>
       <c r="G397" s="3"/>
@@ -10821,7 +10845,7 @@
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
-      <c r="D398" s="33"/>
+      <c r="D398" s="39"/>
       <c r="E398" s="3"/>
       <c r="F398" s="3"/>
       <c r="G398" s="3"/>
@@ -10846,7 +10870,7 @@
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
-      <c r="D399" s="33"/>
+      <c r="D399" s="39"/>
       <c r="E399" s="3"/>
       <c r="F399" s="3"/>
       <c r="G399" s="3"/>
@@ -10871,7 +10895,7 @@
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
-      <c r="D400" s="33"/>
+      <c r="D400" s="39"/>
       <c r="E400" s="3"/>
       <c r="F400" s="3"/>
       <c r="G400" s="3"/>
@@ -10896,7 +10920,7 @@
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
-      <c r="D401" s="33"/>
+      <c r="D401" s="39"/>
       <c r="E401" s="3"/>
       <c r="F401" s="3"/>
       <c r="G401" s="3"/>
@@ -10921,7 +10945,7 @@
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
-      <c r="D402" s="33"/>
+      <c r="D402" s="39"/>
       <c r="E402" s="3"/>
       <c r="F402" s="3"/>
       <c r="G402" s="3"/>
@@ -10946,7 +10970,7 @@
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
-      <c r="D403" s="33"/>
+      <c r="D403" s="39"/>
       <c r="E403" s="3"/>
       <c r="F403" s="3"/>
       <c r="G403" s="3"/>
@@ -10971,7 +10995,7 @@
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
-      <c r="D404" s="33"/>
+      <c r="D404" s="39"/>
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
       <c r="G404" s="3"/>
@@ -10996,7 +11020,7 @@
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
-      <c r="D405" s="33"/>
+      <c r="D405" s="39"/>
       <c r="E405" s="3"/>
       <c r="F405" s="3"/>
       <c r="G405" s="3"/>
@@ -11021,7 +11045,7 @@
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
-      <c r="D406" s="33"/>
+      <c r="D406" s="39"/>
       <c r="E406" s="3"/>
       <c r="F406" s="3"/>
       <c r="G406" s="3"/>
@@ -11046,7 +11070,7 @@
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
-      <c r="D407" s="33"/>
+      <c r="D407" s="39"/>
       <c r="E407" s="3"/>
       <c r="F407" s="3"/>
       <c r="G407" s="3"/>
@@ -11071,7 +11095,7 @@
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
-      <c r="D408" s="33"/>
+      <c r="D408" s="39"/>
       <c r="E408" s="3"/>
       <c r="F408" s="3"/>
       <c r="G408" s="3"/>
@@ -11096,7 +11120,7 @@
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
-      <c r="D409" s="33"/>
+      <c r="D409" s="39"/>
       <c r="E409" s="3"/>
       <c r="F409" s="3"/>
       <c r="G409" s="3"/>
@@ -11121,7 +11145,7 @@
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
-      <c r="D410" s="33"/>
+      <c r="D410" s="39"/>
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
       <c r="G410" s="3"/>
@@ -11146,7 +11170,7 @@
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
-      <c r="D411" s="33"/>
+      <c r="D411" s="39"/>
       <c r="E411" s="3"/>
       <c r="F411" s="3"/>
       <c r="G411" s="3"/>
@@ -11171,7 +11195,7 @@
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
-      <c r="D412" s="33"/>
+      <c r="D412" s="39"/>
       <c r="E412" s="3"/>
       <c r="F412" s="3"/>
       <c r="G412" s="3"/>
@@ -11196,7 +11220,7 @@
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
-      <c r="D413" s="33"/>
+      <c r="D413" s="39"/>
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
       <c r="G413" s="3"/>
@@ -11221,7 +11245,7 @@
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
-      <c r="D414" s="33"/>
+      <c r="D414" s="39"/>
       <c r="E414" s="3"/>
       <c r="F414" s="3"/>
       <c r="G414" s="3"/>
@@ -11246,7 +11270,7 @@
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
-      <c r="D415" s="33"/>
+      <c r="D415" s="39"/>
       <c r="E415" s="3"/>
       <c r="F415" s="3"/>
       <c r="G415" s="3"/>
@@ -11271,7 +11295,7 @@
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
-      <c r="D416" s="33"/>
+      <c r="D416" s="39"/>
       <c r="E416" s="3"/>
       <c r="F416" s="3"/>
       <c r="G416" s="3"/>
@@ -11296,7 +11320,7 @@
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
-      <c r="D417" s="33"/>
+      <c r="D417" s="39"/>
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
       <c r="G417" s="3"/>
@@ -11321,7 +11345,7 @@
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
-      <c r="D418" s="33"/>
+      <c r="D418" s="39"/>
       <c r="E418" s="3"/>
       <c r="F418" s="3"/>
       <c r="G418" s="3"/>
@@ -11346,7 +11370,7 @@
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
-      <c r="D419" s="33"/>
+      <c r="D419" s="39"/>
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
       <c r="G419" s="3"/>
@@ -11371,7 +11395,7 @@
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
-      <c r="D420" s="33"/>
+      <c r="D420" s="39"/>
       <c r="E420" s="3"/>
       <c r="F420" s="3"/>
       <c r="G420" s="3"/>
@@ -11396,7 +11420,7 @@
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
-      <c r="D421" s="33"/>
+      <c r="D421" s="39"/>
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
       <c r="G421" s="3"/>
@@ -11421,7 +11445,7 @@
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
-      <c r="D422" s="33"/>
+      <c r="D422" s="39"/>
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
       <c r="G422" s="3"/>
@@ -11446,7 +11470,7 @@
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
-      <c r="D423" s="33"/>
+      <c r="D423" s="39"/>
       <c r="E423" s="3"/>
       <c r="F423" s="3"/>
       <c r="G423" s="3"/>
@@ -11471,7 +11495,7 @@
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
-      <c r="D424" s="33"/>
+      <c r="D424" s="39"/>
       <c r="E424" s="3"/>
       <c r="F424" s="3"/>
       <c r="G424" s="3"/>
@@ -11496,7 +11520,7 @@
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
-      <c r="D425" s="33"/>
+      <c r="D425" s="39"/>
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
       <c r="G425" s="3"/>
@@ -11521,7 +11545,7 @@
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
-      <c r="D426" s="33"/>
+      <c r="D426" s="39"/>
       <c r="E426" s="3"/>
       <c r="F426" s="3"/>
       <c r="G426" s="3"/>
@@ -11546,7 +11570,7 @@
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
-      <c r="D427" s="33"/>
+      <c r="D427" s="39"/>
       <c r="E427" s="3"/>
       <c r="F427" s="3"/>
       <c r="G427" s="3"/>
@@ -11571,7 +11595,7 @@
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
-      <c r="D428" s="33"/>
+      <c r="D428" s="39"/>
       <c r="E428" s="3"/>
       <c r="F428" s="3"/>
       <c r="G428" s="3"/>
@@ -11596,7 +11620,7 @@
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
-      <c r="D429" s="33"/>
+      <c r="D429" s="39"/>
       <c r="E429" s="3"/>
       <c r="F429" s="3"/>
       <c r="G429" s="3"/>
@@ -11621,7 +11645,7 @@
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
-      <c r="D430" s="33"/>
+      <c r="D430" s="39"/>
       <c r="E430" s="3"/>
       <c r="F430" s="3"/>
       <c r="G430" s="3"/>
@@ -11646,7 +11670,7 @@
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
-      <c r="D431" s="33"/>
+      <c r="D431" s="39"/>
       <c r="E431" s="3"/>
       <c r="F431" s="3"/>
       <c r="G431" s="3"/>
@@ -11671,7 +11695,7 @@
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
-      <c r="D432" s="33"/>
+      <c r="D432" s="39"/>
       <c r="E432" s="3"/>
       <c r="F432" s="3"/>
       <c r="G432" s="3"/>
@@ -11696,7 +11720,7 @@
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
-      <c r="D433" s="33"/>
+      <c r="D433" s="39"/>
       <c r="E433" s="3"/>
       <c r="F433" s="3"/>
       <c r="G433" s="3"/>
@@ -11721,7 +11745,7 @@
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
-      <c r="D434" s="33"/>
+      <c r="D434" s="39"/>
       <c r="E434" s="3"/>
       <c r="F434" s="3"/>
       <c r="G434" s="3"/>
@@ -11746,7 +11770,7 @@
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
-      <c r="D435" s="33"/>
+      <c r="D435" s="39"/>
       <c r="E435" s="3"/>
       <c r="F435" s="3"/>
       <c r="G435" s="3"/>
@@ -11771,7 +11795,7 @@
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
-      <c r="D436" s="33"/>
+      <c r="D436" s="39"/>
       <c r="E436" s="3"/>
       <c r="F436" s="3"/>
       <c r="G436" s="3"/>
@@ -11796,7 +11820,7 @@
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
-      <c r="D437" s="33"/>
+      <c r="D437" s="39"/>
       <c r="E437" s="3"/>
       <c r="F437" s="3"/>
       <c r="G437" s="3"/>
@@ -11821,7 +11845,7 @@
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
-      <c r="D438" s="33"/>
+      <c r="D438" s="39"/>
       <c r="E438" s="3"/>
       <c r="F438" s="3"/>
       <c r="G438" s="3"/>
@@ -11846,7 +11870,7 @@
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
-      <c r="D439" s="33"/>
+      <c r="D439" s="39"/>
       <c r="E439" s="3"/>
       <c r="F439" s="3"/>
       <c r="G439" s="3"/>
@@ -11871,7 +11895,7 @@
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
-      <c r="D440" s="33"/>
+      <c r="D440" s="39"/>
       <c r="E440" s="3"/>
       <c r="F440" s="3"/>
       <c r="G440" s="3"/>
@@ -11896,7 +11920,7 @@
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
-      <c r="D441" s="33"/>
+      <c r="D441" s="39"/>
       <c r="E441" s="3"/>
       <c r="F441" s="3"/>
       <c r="G441" s="3"/>
@@ -11921,7 +11945,7 @@
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
-      <c r="D442" s="33"/>
+      <c r="D442" s="39"/>
       <c r="E442" s="3"/>
       <c r="F442" s="3"/>
       <c r="G442" s="3"/>
@@ -11946,7 +11970,7 @@
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
-      <c r="D443" s="33"/>
+      <c r="D443" s="39"/>
       <c r="E443" s="3"/>
       <c r="F443" s="3"/>
       <c r="G443" s="3"/>
@@ -11971,7 +11995,7 @@
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
-      <c r="D444" s="33"/>
+      <c r="D444" s="39"/>
       <c r="E444" s="3"/>
       <c r="F444" s="3"/>
       <c r="G444" s="3"/>
@@ -11996,7 +12020,7 @@
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
-      <c r="D445" s="33"/>
+      <c r="D445" s="39"/>
       <c r="E445" s="3"/>
       <c r="F445" s="3"/>
       <c r="G445" s="3"/>
@@ -12021,7 +12045,7 @@
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
-      <c r="D446" s="33"/>
+      <c r="D446" s="39"/>
       <c r="E446" s="3"/>
       <c r="F446" s="3"/>
       <c r="G446" s="3"/>
@@ -12046,7 +12070,7 @@
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
-      <c r="D447" s="33"/>
+      <c r="D447" s="39"/>
       <c r="E447" s="3"/>
       <c r="F447" s="3"/>
       <c r="G447" s="3"/>
@@ -12071,7 +12095,7 @@
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
-      <c r="D448" s="33"/>
+      <c r="D448" s="39"/>
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
       <c r="G448" s="3"/>
@@ -12096,7 +12120,7 @@
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
-      <c r="D449" s="33"/>
+      <c r="D449" s="39"/>
       <c r="E449" s="3"/>
       <c r="F449" s="3"/>
       <c r="G449" s="3"/>
@@ -12121,7 +12145,7 @@
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
-      <c r="D450" s="33"/>
+      <c r="D450" s="39"/>
       <c r="E450" s="3"/>
       <c r="F450" s="3"/>
       <c r="G450" s="3"/>
@@ -12146,7 +12170,7 @@
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
-      <c r="D451" s="33"/>
+      <c r="D451" s="39"/>
       <c r="E451" s="3"/>
       <c r="F451" s="3"/>
       <c r="G451" s="3"/>
@@ -12171,7 +12195,7 @@
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
-      <c r="D452" s="33"/>
+      <c r="D452" s="39"/>
       <c r="E452" s="3"/>
       <c r="F452" s="3"/>
       <c r="G452" s="3"/>
@@ -12196,7 +12220,7 @@
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
-      <c r="D453" s="33"/>
+      <c r="D453" s="39"/>
       <c r="E453" s="3"/>
       <c r="F453" s="3"/>
       <c r="G453" s="3"/>
@@ -12221,7 +12245,7 @@
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
-      <c r="D454" s="33"/>
+      <c r="D454" s="39"/>
       <c r="E454" s="3"/>
       <c r="F454" s="3"/>
       <c r="G454" s="3"/>
@@ -12246,7 +12270,7 @@
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
-      <c r="D455" s="33"/>
+      <c r="D455" s="39"/>
       <c r="E455" s="3"/>
       <c r="F455" s="3"/>
       <c r="G455" s="3"/>
@@ -12271,7 +12295,7 @@
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
-      <c r="D456" s="33"/>
+      <c r="D456" s="39"/>
       <c r="E456" s="3"/>
       <c r="F456" s="3"/>
       <c r="G456" s="3"/>
@@ -12296,7 +12320,7 @@
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
-      <c r="D457" s="33"/>
+      <c r="D457" s="39"/>
       <c r="E457" s="3"/>
       <c r="F457" s="3"/>
       <c r="G457" s="3"/>
@@ -12321,7 +12345,7 @@
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
-      <c r="D458" s="33"/>
+      <c r="D458" s="39"/>
       <c r="E458" s="3"/>
       <c r="F458" s="3"/>
       <c r="G458" s="3"/>
@@ -12346,7 +12370,7 @@
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
-      <c r="D459" s="33"/>
+      <c r="D459" s="39"/>
       <c r="E459" s="3"/>
       <c r="F459" s="3"/>
       <c r="G459" s="3"/>
@@ -12371,7 +12395,7 @@
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
-      <c r="D460" s="33"/>
+      <c r="D460" s="39"/>
       <c r="E460" s="3"/>
       <c r="F460" s="3"/>
       <c r="G460" s="3"/>
@@ -12396,7 +12420,7 @@
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
-      <c r="D461" s="33"/>
+      <c r="D461" s="39"/>
       <c r="E461" s="3"/>
       <c r="F461" s="3"/>
       <c r="G461" s="3"/>
@@ -12421,7 +12445,7 @@
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
-      <c r="D462" s="33"/>
+      <c r="D462" s="39"/>
       <c r="E462" s="3"/>
       <c r="F462" s="3"/>
       <c r="G462" s="3"/>
@@ -12446,7 +12470,7 @@
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
-      <c r="D463" s="33"/>
+      <c r="D463" s="39"/>
       <c r="E463" s="3"/>
       <c r="F463" s="3"/>
       <c r="G463" s="3"/>
@@ -12471,7 +12495,7 @@
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
-      <c r="D464" s="33"/>
+      <c r="D464" s="39"/>
       <c r="E464" s="3"/>
       <c r="F464" s="3"/>
       <c r="G464" s="3"/>
@@ -12496,7 +12520,7 @@
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
-      <c r="D465" s="33"/>
+      <c r="D465" s="39"/>
       <c r="E465" s="3"/>
       <c r="F465" s="3"/>
       <c r="G465" s="3"/>
@@ -12521,7 +12545,7 @@
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
-      <c r="D466" s="33"/>
+      <c r="D466" s="39"/>
       <c r="E466" s="3"/>
       <c r="F466" s="3"/>
       <c r="G466" s="3"/>
@@ -12546,7 +12570,7 @@
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
-      <c r="D467" s="33"/>
+      <c r="D467" s="39"/>
       <c r="E467" s="3"/>
       <c r="F467" s="3"/>
       <c r="G467" s="3"/>
@@ -12571,7 +12595,7 @@
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
-      <c r="D468" s="33"/>
+      <c r="D468" s="39"/>
       <c r="E468" s="3"/>
       <c r="F468" s="3"/>
       <c r="G468" s="3"/>
@@ -12596,7 +12620,7 @@
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
-      <c r="D469" s="33"/>
+      <c r="D469" s="39"/>
       <c r="E469" s="3"/>
       <c r="F469" s="3"/>
       <c r="G469" s="3"/>
@@ -12621,7 +12645,7 @@
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
-      <c r="D470" s="33"/>
+      <c r="D470" s="39"/>
       <c r="E470" s="3"/>
       <c r="F470" s="3"/>
       <c r="G470" s="3"/>
@@ -12646,7 +12670,7 @@
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
-      <c r="D471" s="33"/>
+      <c r="D471" s="39"/>
       <c r="E471" s="3"/>
       <c r="F471" s="3"/>
       <c r="G471" s="3"/>
@@ -12671,7 +12695,7 @@
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
-      <c r="D472" s="33"/>
+      <c r="D472" s="39"/>
       <c r="E472" s="3"/>
       <c r="F472" s="3"/>
       <c r="G472" s="3"/>
@@ -12696,7 +12720,7 @@
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
-      <c r="D473" s="33"/>
+      <c r="D473" s="39"/>
       <c r="E473" s="3"/>
       <c r="F473" s="3"/>
       <c r="G473" s="3"/>
@@ -12721,7 +12745,7 @@
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
-      <c r="D474" s="33"/>
+      <c r="D474" s="39"/>
       <c r="E474" s="3"/>
       <c r="F474" s="3"/>
       <c r="G474" s="3"/>
@@ -12746,7 +12770,7 @@
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
-      <c r="D475" s="33"/>
+      <c r="D475" s="39"/>
       <c r="E475" s="3"/>
       <c r="F475" s="3"/>
       <c r="G475" s="3"/>
@@ -12771,7 +12795,7 @@
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
-      <c r="D476" s="33"/>
+      <c r="D476" s="39"/>
       <c r="E476" s="3"/>
       <c r="F476" s="3"/>
       <c r="G476" s="3"/>
@@ -12796,7 +12820,7 @@
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
-      <c r="D477" s="33"/>
+      <c r="D477" s="39"/>
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
       <c r="G477" s="3"/>
@@ -12821,7 +12845,7 @@
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
-      <c r="D478" s="33"/>
+      <c r="D478" s="39"/>
       <c r="E478" s="3"/>
       <c r="F478" s="3"/>
       <c r="G478" s="3"/>
@@ -12846,7 +12870,7 @@
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
-      <c r="D479" s="33"/>
+      <c r="D479" s="39"/>
       <c r="E479" s="3"/>
       <c r="F479" s="3"/>
       <c r="G479" s="3"/>
@@ -12871,7 +12895,7 @@
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
-      <c r="D480" s="33"/>
+      <c r="D480" s="39"/>
       <c r="E480" s="3"/>
       <c r="F480" s="3"/>
       <c r="G480" s="3"/>
@@ -12896,7 +12920,7 @@
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
-      <c r="D481" s="33"/>
+      <c r="D481" s="39"/>
       <c r="E481" s="3"/>
       <c r="F481" s="3"/>
       <c r="G481" s="3"/>
@@ -12921,7 +12945,7 @@
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
-      <c r="D482" s="33"/>
+      <c r="D482" s="39"/>
       <c r="E482" s="3"/>
       <c r="F482" s="3"/>
       <c r="G482" s="3"/>
@@ -12946,7 +12970,7 @@
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
-      <c r="D483" s="33"/>
+      <c r="D483" s="39"/>
       <c r="E483" s="3"/>
       <c r="F483" s="3"/>
       <c r="G483" s="3"/>
@@ -12971,7 +12995,7 @@
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
-      <c r="D484" s="33"/>
+      <c r="D484" s="39"/>
       <c r="E484" s="3"/>
       <c r="F484" s="3"/>
       <c r="G484" s="3"/>
@@ -12996,7 +13020,7 @@
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
-      <c r="D485" s="33"/>
+      <c r="D485" s="39"/>
       <c r="E485" s="3"/>
       <c r="F485" s="3"/>
       <c r="G485" s="3"/>
@@ -13021,7 +13045,7 @@
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
-      <c r="D486" s="33"/>
+      <c r="D486" s="39"/>
       <c r="E486" s="3"/>
       <c r="F486" s="3"/>
       <c r="G486" s="3"/>
@@ -13046,7 +13070,7 @@
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
-      <c r="D487" s="33"/>
+      <c r="D487" s="39"/>
       <c r="E487" s="3"/>
       <c r="F487" s="3"/>
       <c r="G487" s="3"/>
@@ -13071,7 +13095,7 @@
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
-      <c r="D488" s="33"/>
+      <c r="D488" s="39"/>
       <c r="E488" s="3"/>
       <c r="F488" s="3"/>
       <c r="G488" s="3"/>
@@ -13096,7 +13120,7 @@
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
-      <c r="D489" s="33"/>
+      <c r="D489" s="39"/>
       <c r="E489" s="3"/>
       <c r="F489" s="3"/>
       <c r="G489" s="3"/>
@@ -13121,7 +13145,7 @@
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
-      <c r="D490" s="33"/>
+      <c r="D490" s="39"/>
       <c r="E490" s="3"/>
       <c r="F490" s="3"/>
       <c r="G490" s="3"/>
@@ -13146,7 +13170,7 @@
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
-      <c r="D491" s="33"/>
+      <c r="D491" s="39"/>
       <c r="E491" s="3"/>
       <c r="F491" s="3"/>
       <c r="G491" s="3"/>
@@ -13171,7 +13195,7 @@
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
-      <c r="D492" s="33"/>
+      <c r="D492" s="39"/>
       <c r="E492" s="3"/>
       <c r="F492" s="3"/>
       <c r="G492" s="3"/>
@@ -13196,7 +13220,7 @@
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
-      <c r="D493" s="33"/>
+      <c r="D493" s="39"/>
       <c r="E493" s="3"/>
       <c r="F493" s="3"/>
       <c r="G493" s="3"/>
@@ -13221,7 +13245,7 @@
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
-      <c r="D494" s="33"/>
+      <c r="D494" s="39"/>
       <c r="E494" s="3"/>
       <c r="F494" s="3"/>
       <c r="G494" s="3"/>
@@ -13246,7 +13270,7 @@
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
-      <c r="D495" s="33"/>
+      <c r="D495" s="39"/>
       <c r="E495" s="3"/>
       <c r="F495" s="3"/>
       <c r="G495" s="3"/>
@@ -13271,7 +13295,7 @@
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
-      <c r="D496" s="33"/>
+      <c r="D496" s="39"/>
       <c r="E496" s="3"/>
       <c r="F496" s="3"/>
       <c r="G496" s="3"/>
@@ -13296,7 +13320,7 @@
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
-      <c r="D497" s="33"/>
+      <c r="D497" s="39"/>
       <c r="E497" s="3"/>
       <c r="F497" s="3"/>
       <c r="G497" s="3"/>
@@ -13321,7 +13345,7 @@
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
-      <c r="D498" s="33"/>
+      <c r="D498" s="39"/>
       <c r="E498" s="3"/>
       <c r="F498" s="3"/>
       <c r="G498" s="3"/>
@@ -13346,7 +13370,7 @@
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
-      <c r="D499" s="33"/>
+      <c r="D499" s="39"/>
       <c r="E499" s="3"/>
       <c r="F499" s="3"/>
       <c r="G499" s="3"/>
@@ -13371,7 +13395,7 @@
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
-      <c r="D500" s="33"/>
+      <c r="D500" s="39"/>
       <c r="E500" s="3"/>
       <c r="F500" s="3"/>
       <c r="G500" s="3"/>
@@ -13396,7 +13420,7 @@
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
-      <c r="D501" s="33"/>
+      <c r="D501" s="39"/>
       <c r="E501" s="3"/>
       <c r="F501" s="3"/>
       <c r="G501" s="3"/>
@@ -13421,7 +13445,7 @@
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
-      <c r="D502" s="33"/>
+      <c r="D502" s="39"/>
       <c r="E502" s="3"/>
       <c r="F502" s="3"/>
       <c r="G502" s="3"/>
@@ -13446,7 +13470,7 @@
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
-      <c r="D503" s="33"/>
+      <c r="D503" s="39"/>
       <c r="E503" s="3"/>
       <c r="F503" s="3"/>
       <c r="G503" s="3"/>
@@ -13471,7 +13495,7 @@
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
-      <c r="D504" s="33"/>
+      <c r="D504" s="39"/>
       <c r="E504" s="3"/>
       <c r="F504" s="3"/>
       <c r="G504" s="3"/>
@@ -13496,7 +13520,7 @@
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
-      <c r="D505" s="33"/>
+      <c r="D505" s="39"/>
       <c r="E505" s="3"/>
       <c r="F505" s="3"/>
       <c r="G505" s="3"/>
@@ -13521,7 +13545,7 @@
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
-      <c r="D506" s="33"/>
+      <c r="D506" s="39"/>
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
       <c r="G506" s="3"/>
@@ -13546,7 +13570,7 @@
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
-      <c r="D507" s="33"/>
+      <c r="D507" s="39"/>
       <c r="E507" s="3"/>
       <c r="F507" s="3"/>
       <c r="G507" s="3"/>
@@ -13571,7 +13595,7 @@
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
-      <c r="D508" s="33"/>
+      <c r="D508" s="39"/>
       <c r="E508" s="3"/>
       <c r="F508" s="3"/>
       <c r="G508" s="3"/>
@@ -13596,7 +13620,7 @@
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
-      <c r="D509" s="33"/>
+      <c r="D509" s="39"/>
       <c r="E509" s="3"/>
       <c r="F509" s="3"/>
       <c r="G509" s="3"/>
@@ -13621,7 +13645,7 @@
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
-      <c r="D510" s="33"/>
+      <c r="D510" s="39"/>
       <c r="E510" s="3"/>
       <c r="F510" s="3"/>
       <c r="G510" s="3"/>
@@ -13646,7 +13670,7 @@
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
-      <c r="D511" s="33"/>
+      <c r="D511" s="39"/>
       <c r="E511" s="3"/>
       <c r="F511" s="3"/>
       <c r="G511" s="3"/>
@@ -13671,7 +13695,7 @@
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
-      <c r="D512" s="33"/>
+      <c r="D512" s="39"/>
       <c r="E512" s="3"/>
       <c r="F512" s="3"/>
       <c r="G512" s="3"/>
@@ -13696,7 +13720,7 @@
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
-      <c r="D513" s="33"/>
+      <c r="D513" s="39"/>
       <c r="E513" s="3"/>
       <c r="F513" s="3"/>
       <c r="G513" s="3"/>
@@ -13721,7 +13745,7 @@
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
-      <c r="D514" s="33"/>
+      <c r="D514" s="39"/>
       <c r="E514" s="3"/>
       <c r="F514" s="3"/>
       <c r="G514" s="3"/>
@@ -13746,7 +13770,7 @@
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
-      <c r="D515" s="33"/>
+      <c r="D515" s="39"/>
       <c r="E515" s="3"/>
       <c r="F515" s="3"/>
       <c r="G515" s="3"/>
@@ -13771,7 +13795,7 @@
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
-      <c r="D516" s="33"/>
+      <c r="D516" s="39"/>
       <c r="E516" s="3"/>
       <c r="F516" s="3"/>
       <c r="G516" s="3"/>
@@ -13796,7 +13820,7 @@
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
-      <c r="D517" s="33"/>
+      <c r="D517" s="39"/>
       <c r="E517" s="3"/>
       <c r="F517" s="3"/>
       <c r="G517" s="3"/>
@@ -13821,7 +13845,7 @@
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
-      <c r="D518" s="33"/>
+      <c r="D518" s="39"/>
       <c r="E518" s="3"/>
       <c r="F518" s="3"/>
       <c r="G518" s="3"/>
@@ -13846,7 +13870,7 @@
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
-      <c r="D519" s="33"/>
+      <c r="D519" s="39"/>
       <c r="E519" s="3"/>
       <c r="F519" s="3"/>
       <c r="G519" s="3"/>
@@ -13871,7 +13895,7 @@
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
-      <c r="D520" s="33"/>
+      <c r="D520" s="39"/>
       <c r="E520" s="3"/>
       <c r="F520" s="3"/>
       <c r="G520" s="3"/>
@@ -13896,7 +13920,7 @@
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
-      <c r="D521" s="33"/>
+      <c r="D521" s="39"/>
       <c r="E521" s="3"/>
       <c r="F521" s="3"/>
       <c r="G521" s="3"/>
@@ -13921,7 +13945,7 @@
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
-      <c r="D522" s="33"/>
+      <c r="D522" s="39"/>
       <c r="E522" s="3"/>
       <c r="F522" s="3"/>
       <c r="G522" s="3"/>
@@ -13946,7 +13970,7 @@
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
-      <c r="D523" s="33"/>
+      <c r="D523" s="39"/>
       <c r="E523" s="3"/>
       <c r="F523" s="3"/>
       <c r="G523" s="3"/>
@@ -13971,7 +13995,7 @@
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
-      <c r="D524" s="33"/>
+      <c r="D524" s="39"/>
       <c r="E524" s="3"/>
       <c r="F524" s="3"/>
       <c r="G524" s="3"/>
@@ -13996,7 +14020,7 @@
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
-      <c r="D525" s="33"/>
+      <c r="D525" s="39"/>
       <c r="E525" s="3"/>
       <c r="F525" s="3"/>
       <c r="G525" s="3"/>
@@ -14021,7 +14045,7 @@
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
-      <c r="D526" s="33"/>
+      <c r="D526" s="39"/>
       <c r="E526" s="3"/>
       <c r="F526" s="3"/>
       <c r="G526" s="3"/>
@@ -14046,7 +14070,7 @@
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
-      <c r="D527" s="33"/>
+      <c r="D527" s="39"/>
       <c r="E527" s="3"/>
       <c r="F527" s="3"/>
       <c r="G527" s="3"/>
@@ -14071,7 +14095,7 @@
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
-      <c r="D528" s="33"/>
+      <c r="D528" s="39"/>
       <c r="E528" s="3"/>
       <c r="F528" s="3"/>
       <c r="G528" s="3"/>
@@ -14096,7 +14120,7 @@
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
-      <c r="D529" s="33"/>
+      <c r="D529" s="39"/>
       <c r="E529" s="3"/>
       <c r="F529" s="3"/>
       <c r="G529" s="3"/>
@@ -14121,7 +14145,7 @@
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
-      <c r="D530" s="33"/>
+      <c r="D530" s="39"/>
       <c r="E530" s="3"/>
       <c r="F530" s="3"/>
       <c r="G530" s="3"/>
@@ -14146,7 +14170,7 @@
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
-      <c r="D531" s="33"/>
+      <c r="D531" s="39"/>
       <c r="E531" s="3"/>
       <c r="F531" s="3"/>
       <c r="G531" s="3"/>
@@ -14171,7 +14195,7 @@
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
-      <c r="D532" s="33"/>
+      <c r="D532" s="39"/>
       <c r="E532" s="3"/>
       <c r="F532" s="3"/>
       <c r="G532" s="3"/>
@@ -14196,7 +14220,7 @@
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
-      <c r="D533" s="33"/>
+      <c r="D533" s="39"/>
       <c r="E533" s="3"/>
       <c r="F533" s="3"/>
       <c r="G533" s="3"/>
@@ -14221,7 +14245,7 @@
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
-      <c r="D534" s="33"/>
+      <c r="D534" s="39"/>
       <c r="E534" s="3"/>
       <c r="F534" s="3"/>
       <c r="G534" s="3"/>
@@ -14246,7 +14270,7 @@
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
-      <c r="D535" s="33"/>
+      <c r="D535" s="39"/>
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
       <c r="G535" s="3"/>
@@ -14271,7 +14295,7 @@
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
-      <c r="D536" s="33"/>
+      <c r="D536" s="39"/>
       <c r="E536" s="3"/>
       <c r="F536" s="3"/>
       <c r="G536" s="3"/>
@@ -14296,7 +14320,7 @@
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
-      <c r="D537" s="33"/>
+      <c r="D537" s="39"/>
       <c r="E537" s="3"/>
       <c r="F537" s="3"/>
       <c r="G537" s="3"/>
@@ -14321,7 +14345,7 @@
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
-      <c r="D538" s="33"/>
+      <c r="D538" s="39"/>
       <c r="E538" s="3"/>
       <c r="F538" s="3"/>
       <c r="G538" s="3"/>
@@ -14346,7 +14370,7 @@
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
-      <c r="D539" s="33"/>
+      <c r="D539" s="39"/>
       <c r="E539" s="3"/>
       <c r="F539" s="3"/>
       <c r="G539" s="3"/>
@@ -14371,7 +14395,7 @@
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
-      <c r="D540" s="33"/>
+      <c r="D540" s="39"/>
       <c r="E540" s="3"/>
       <c r="F540" s="3"/>
       <c r="G540" s="3"/>
@@ -14396,7 +14420,7 @@
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
-      <c r="D541" s="33"/>
+      <c r="D541" s="39"/>
       <c r="E541" s="3"/>
       <c r="F541" s="3"/>
       <c r="G541" s="3"/>
@@ -14421,7 +14445,7 @@
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
-      <c r="D542" s="33"/>
+      <c r="D542" s="39"/>
       <c r="E542" s="3"/>
       <c r="F542" s="3"/>
       <c r="G542" s="3"/>
@@ -14446,7 +14470,7 @@
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
-      <c r="D543" s="33"/>
+      <c r="D543" s="39"/>
       <c r="E543" s="3"/>
       <c r="F543" s="3"/>
       <c r="G543" s="3"/>
@@ -14471,7 +14495,7 @@
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
-      <c r="D544" s="33"/>
+      <c r="D544" s="39"/>
       <c r="E544" s="3"/>
       <c r="F544" s="3"/>
       <c r="G544" s="3"/>
@@ -14496,7 +14520,7 @@
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
-      <c r="D545" s="33"/>
+      <c r="D545" s="39"/>
       <c r="E545" s="3"/>
       <c r="F545" s="3"/>
       <c r="G545" s="3"/>
@@ -14521,7 +14545,7 @@
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
-      <c r="D546" s="33"/>
+      <c r="D546" s="39"/>
       <c r="E546" s="3"/>
       <c r="F546" s="3"/>
       <c r="G546" s="3"/>
@@ -14546,7 +14570,7 @@
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
-      <c r="D547" s="33"/>
+      <c r="D547" s="39"/>
       <c r="E547" s="3"/>
       <c r="F547" s="3"/>
       <c r="G547" s="3"/>
@@ -14571,7 +14595,7 @@
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
-      <c r="D548" s="33"/>
+      <c r="D548" s="39"/>
       <c r="E548" s="3"/>
       <c r="F548" s="3"/>
       <c r="G548" s="3"/>
@@ -14596,7 +14620,7 @@
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
-      <c r="D549" s="33"/>
+      <c r="D549" s="39"/>
       <c r="E549" s="3"/>
       <c r="F549" s="3"/>
       <c r="G549" s="3"/>
@@ -14621,7 +14645,7 @@
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
-      <c r="D550" s="33"/>
+      <c r="D550" s="39"/>
       <c r="E550" s="3"/>
       <c r="F550" s="3"/>
       <c r="G550" s="3"/>
@@ -14646,7 +14670,7 @@
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
-      <c r="D551" s="33"/>
+      <c r="D551" s="39"/>
       <c r="E551" s="3"/>
       <c r="F551" s="3"/>
       <c r="G551" s="3"/>
@@ -14671,7 +14695,7 @@
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
-      <c r="D552" s="33"/>
+      <c r="D552" s="39"/>
       <c r="E552" s="3"/>
       <c r="F552" s="3"/>
       <c r="G552" s="3"/>
@@ -14696,7 +14720,7 @@
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
-      <c r="D553" s="33"/>
+      <c r="D553" s="39"/>
       <c r="E553" s="3"/>
       <c r="F553" s="3"/>
       <c r="G553" s="3"/>
@@ -14721,7 +14745,7 @@
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
-      <c r="D554" s="33"/>
+      <c r="D554" s="39"/>
       <c r="E554" s="3"/>
       <c r="F554" s="3"/>
       <c r="G554" s="3"/>
@@ -14746,7 +14770,7 @@
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
-      <c r="D555" s="33"/>
+      <c r="D555" s="39"/>
       <c r="E555" s="3"/>
       <c r="F555" s="3"/>
       <c r="G555" s="3"/>
@@ -14771,7 +14795,7 @@
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
-      <c r="D556" s="33"/>
+      <c r="D556" s="39"/>
       <c r="E556" s="3"/>
       <c r="F556" s="3"/>
       <c r="G556" s="3"/>
@@ -14796,7 +14820,7 @@
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
-      <c r="D557" s="33"/>
+      <c r="D557" s="39"/>
       <c r="E557" s="3"/>
       <c r="F557" s="3"/>
       <c r="G557" s="3"/>
@@ -14821,7 +14845,7 @@
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
-      <c r="D558" s="33"/>
+      <c r="D558" s="39"/>
       <c r="E558" s="3"/>
       <c r="F558" s="3"/>
       <c r="G558" s="3"/>
@@ -14846,7 +14870,7 @@
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
-      <c r="D559" s="33"/>
+      <c r="D559" s="39"/>
       <c r="E559" s="3"/>
       <c r="F559" s="3"/>
       <c r="G559" s="3"/>
@@ -14871,7 +14895,7 @@
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
-      <c r="D560" s="33"/>
+      <c r="D560" s="39"/>
       <c r="E560" s="3"/>
       <c r="F560" s="3"/>
       <c r="G560" s="3"/>
@@ -14896,7 +14920,7 @@
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
-      <c r="D561" s="33"/>
+      <c r="D561" s="39"/>
       <c r="E561" s="3"/>
       <c r="F561" s="3"/>
       <c r="G561" s="3"/>
@@ -14921,7 +14945,7 @@
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
-      <c r="D562" s="33"/>
+      <c r="D562" s="39"/>
       <c r="E562" s="3"/>
       <c r="F562" s="3"/>
       <c r="G562" s="3"/>
@@ -14946,7 +14970,7 @@
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
-      <c r="D563" s="33"/>
+      <c r="D563" s="39"/>
       <c r="E563" s="3"/>
       <c r="F563" s="3"/>
       <c r="G563" s="3"/>
@@ -14971,7 +14995,7 @@
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
-      <c r="D564" s="33"/>
+      <c r="D564" s="39"/>
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
       <c r="G564" s="3"/>
@@ -14996,7 +15020,7 @@
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
-      <c r="D565" s="33"/>
+      <c r="D565" s="39"/>
       <c r="E565" s="3"/>
       <c r="F565" s="3"/>
       <c r="G565" s="3"/>
@@ -15021,7 +15045,7 @@
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
-      <c r="D566" s="33"/>
+      <c r="D566" s="39"/>
       <c r="E566" s="3"/>
       <c r="F566" s="3"/>
       <c r="G566" s="3"/>
@@ -15046,7 +15070,7 @@
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
-      <c r="D567" s="33"/>
+      <c r="D567" s="39"/>
       <c r="E567" s="3"/>
       <c r="F567" s="3"/>
       <c r="G567" s="3"/>
@@ -15071,7 +15095,7 @@
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
-      <c r="D568" s="33"/>
+      <c r="D568" s="39"/>
       <c r="E568" s="3"/>
       <c r="F568" s="3"/>
       <c r="G568" s="3"/>
@@ -15096,7 +15120,7 @@
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
-      <c r="D569" s="33"/>
+      <c r="D569" s="39"/>
       <c r="E569" s="3"/>
       <c r="F569" s="3"/>
       <c r="G569" s="3"/>
@@ -15121,7 +15145,7 @@
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
-      <c r="D570" s="33"/>
+      <c r="D570" s="39"/>
       <c r="E570" s="3"/>
       <c r="F570" s="3"/>
       <c r="G570" s="3"/>
@@ -15146,7 +15170,7 @@
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
-      <c r="D571" s="33"/>
+      <c r="D571" s="39"/>
       <c r="E571" s="3"/>
       <c r="F571" s="3"/>
       <c r="G571" s="3"/>
@@ -15171,7 +15195,7 @@
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
-      <c r="D572" s="33"/>
+      <c r="D572" s="39"/>
       <c r="E572" s="3"/>
       <c r="F572" s="3"/>
       <c r="G572" s="3"/>
@@ -15196,7 +15220,7 @@
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
-      <c r="D573" s="33"/>
+      <c r="D573" s="39"/>
       <c r="E573" s="3"/>
       <c r="F573" s="3"/>
       <c r="G573" s="3"/>
@@ -15221,7 +15245,7 @@
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
-      <c r="D574" s="33"/>
+      <c r="D574" s="39"/>
       <c r="E574" s="3"/>
       <c r="F574" s="3"/>
       <c r="G574" s="3"/>
@@ -15246,7 +15270,7 @@
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
-      <c r="D575" s="33"/>
+      <c r="D575" s="39"/>
       <c r="E575" s="3"/>
       <c r="F575" s="3"/>
       <c r="G575" s="3"/>
@@ -15271,7 +15295,7 @@
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
-      <c r="D576" s="33"/>
+      <c r="D576" s="39"/>
       <c r="E576" s="3"/>
       <c r="F576" s="3"/>
       <c r="G576" s="3"/>
@@ -15296,7 +15320,7 @@
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
-      <c r="D577" s="33"/>
+      <c r="D577" s="39"/>
       <c r="E577" s="3"/>
       <c r="F577" s="3"/>
       <c r="G577" s="3"/>
@@ -15321,7 +15345,7 @@
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
-      <c r="D578" s="33"/>
+      <c r="D578" s="39"/>
       <c r="E578" s="3"/>
       <c r="F578" s="3"/>
       <c r="G578" s="3"/>
@@ -15346,7 +15370,7 @@
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
-      <c r="D579" s="33"/>
+      <c r="D579" s="39"/>
       <c r="E579" s="3"/>
       <c r="F579" s="3"/>
       <c r="G579" s="3"/>
@@ -15371,7 +15395,7 @@
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
-      <c r="D580" s="33"/>
+      <c r="D580" s="39"/>
       <c r="E580" s="3"/>
       <c r="F580" s="3"/>
       <c r="G580" s="3"/>
@@ -15396,7 +15420,7 @@
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
-      <c r="D581" s="33"/>
+      <c r="D581" s="39"/>
       <c r="E581" s="3"/>
       <c r="F581" s="3"/>
       <c r="G581" s="3"/>
@@ -15421,7 +15445,7 @@
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
-      <c r="D582" s="33"/>
+      <c r="D582" s="39"/>
       <c r="E582" s="3"/>
       <c r="F582" s="3"/>
       <c r="G582" s="3"/>
@@ -15446,7 +15470,7 @@
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
-      <c r="D583" s="33"/>
+      <c r="D583" s="39"/>
       <c r="E583" s="3"/>
       <c r="F583" s="3"/>
       <c r="G583" s="3"/>
@@ -15471,7 +15495,7 @@
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
-      <c r="D584" s="33"/>
+      <c r="D584" s="39"/>
       <c r="E584" s="3"/>
       <c r="F584" s="3"/>
       <c r="G584" s="3"/>
@@ -15496,7 +15520,7 @@
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
-      <c r="D585" s="33"/>
+      <c r="D585" s="39"/>
       <c r="E585" s="3"/>
       <c r="F585" s="3"/>
       <c r="G585" s="3"/>
@@ -15521,7 +15545,7 @@
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
-      <c r="D586" s="33"/>
+      <c r="D586" s="39"/>
       <c r="E586" s="3"/>
       <c r="F586" s="3"/>
       <c r="G586" s="3"/>
@@ -15546,7 +15570,7 @@
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
-      <c r="D587" s="33"/>
+      <c r="D587" s="39"/>
       <c r="E587" s="3"/>
       <c r="F587" s="3"/>
       <c r="G587" s="3"/>
@@ -15571,7 +15595,7 @@
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
-      <c r="D588" s="33"/>
+      <c r="D588" s="39"/>
       <c r="E588" s="3"/>
       <c r="F588" s="3"/>
       <c r="G588" s="3"/>
@@ -15596,7 +15620,7 @@
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
-      <c r="D589" s="33"/>
+      <c r="D589" s="39"/>
       <c r="E589" s="3"/>
       <c r="F589" s="3"/>
       <c r="G589" s="3"/>
@@ -15621,7 +15645,7 @@
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
-      <c r="D590" s="33"/>
+      <c r="D590" s="39"/>
       <c r="E590" s="3"/>
       <c r="F590" s="3"/>
       <c r="G590" s="3"/>
@@ -15646,7 +15670,7 @@
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
-      <c r="D591" s="33"/>
+      <c r="D591" s="39"/>
       <c r="E591" s="3"/>
       <c r="F591" s="3"/>
       <c r="G591" s="3"/>
@@ -15671,7 +15695,7 @@
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
-      <c r="D592" s="33"/>
+      <c r="D592" s="39"/>
       <c r="E592" s="3"/>
       <c r="F592" s="3"/>
       <c r="G592" s="3"/>
@@ -15696,7 +15720,7 @@
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
-      <c r="D593" s="33"/>
+      <c r="D593" s="39"/>
       <c r="E593" s="3"/>
       <c r="F593" s="3"/>
       <c r="G593" s="3"/>
@@ -15721,7 +15745,7 @@
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
-      <c r="D594" s="33"/>
+      <c r="D594" s="39"/>
       <c r="E594" s="3"/>
       <c r="F594" s="3"/>
       <c r="G594" s="3"/>
@@ -15746,7 +15770,7 @@
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
-      <c r="D595" s="33"/>
+      <c r="D595" s="39"/>
       <c r="E595" s="3"/>
       <c r="F595" s="3"/>
       <c r="G595" s="3"/>
@@ -15771,7 +15795,7 @@
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
-      <c r="D596" s="33"/>
+      <c r="D596" s="39"/>
       <c r="E596" s="3"/>
       <c r="F596" s="3"/>
       <c r="G596" s="3"/>
@@ -15796,7 +15820,7 @@
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
-      <c r="D597" s="33"/>
+      <c r="D597" s="39"/>
       <c r="E597" s="3"/>
       <c r="F597" s="3"/>
       <c r="G597" s="3"/>
@@ -15821,7 +15845,7 @@
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
-      <c r="D598" s="33"/>
+      <c r="D598" s="39"/>
       <c r="E598" s="3"/>
       <c r="F598" s="3"/>
       <c r="G598" s="3"/>
@@ -15846,7 +15870,7 @@
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
-      <c r="D599" s="33"/>
+      <c r="D599" s="39"/>
       <c r="E599" s="3"/>
       <c r="F599" s="3"/>
       <c r="G599" s="3"/>
@@ -15871,7 +15895,7 @@
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
-      <c r="D600" s="33"/>
+      <c r="D600" s="39"/>
       <c r="E600" s="3"/>
       <c r="F600" s="3"/>
       <c r="G600" s="3"/>
@@ -15896,7 +15920,7 @@
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
-      <c r="D601" s="33"/>
+      <c r="D601" s="39"/>
       <c r="E601" s="3"/>
       <c r="F601" s="3"/>
       <c r="G601" s="3"/>
@@ -15921,7 +15945,7 @@
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
-      <c r="D602" s="33"/>
+      <c r="D602" s="39"/>
       <c r="E602" s="3"/>
       <c r="F602" s="3"/>
       <c r="G602" s="3"/>
@@ -15946,7 +15970,7 @@
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
-      <c r="D603" s="33"/>
+      <c r="D603" s="39"/>
       <c r="E603" s="3"/>
       <c r="F603" s="3"/>
       <c r="G603" s="3"/>
@@ -15971,7 +15995,7 @@
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
-      <c r="D604" s="33"/>
+      <c r="D604" s="39"/>
       <c r="E604" s="3"/>
       <c r="F604" s="3"/>
       <c r="G604" s="3"/>
@@ -15996,7 +16020,7 @@
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
-      <c r="D605" s="33"/>
+      <c r="D605" s="39"/>
       <c r="E605" s="3"/>
       <c r="F605" s="3"/>
       <c r="G605" s="3"/>
@@ -16021,7 +16045,7 @@
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
-      <c r="D606" s="33"/>
+      <c r="D606" s="39"/>
       <c r="E606" s="3"/>
       <c r="F606" s="3"/>
       <c r="G606" s="3"/>
@@ -16046,7 +16070,7 @@
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
-      <c r="D607" s="33"/>
+      <c r="D607" s="39"/>
       <c r="E607" s="3"/>
       <c r="F607" s="3"/>
       <c r="G607" s="3"/>
@@ -16071,7 +16095,7 @@
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
-      <c r="D608" s="33"/>
+      <c r="D608" s="39"/>
       <c r="E608" s="3"/>
       <c r="F608" s="3"/>
       <c r="G608" s="3"/>
@@ -16096,7 +16120,7 @@
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
-      <c r="D609" s="33"/>
+      <c r="D609" s="39"/>
       <c r="E609" s="3"/>
       <c r="F609" s="3"/>
       <c r="G609" s="3"/>
@@ -16121,7 +16145,7 @@
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
-      <c r="D610" s="33"/>
+      <c r="D610" s="39"/>
       <c r="E610" s="3"/>
       <c r="F610" s="3"/>
       <c r="G610" s="3"/>
@@ -16146,7 +16170,7 @@
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
-      <c r="D611" s="33"/>
+      <c r="D611" s="39"/>
       <c r="E611" s="3"/>
       <c r="F611" s="3"/>
       <c r="G611" s="3"/>
@@ -16171,7 +16195,7 @@
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
-      <c r="D612" s="33"/>
+      <c r="D612" s="39"/>
       <c r="E612" s="3"/>
       <c r="F612" s="3"/>
       <c r="G612" s="3"/>
@@ -16196,7 +16220,7 @@
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
-      <c r="D613" s="33"/>
+      <c r="D613" s="39"/>
       <c r="E613" s="3"/>
       <c r="F613" s="3"/>
       <c r="G613" s="3"/>
@@ -16221,7 +16245,7 @@
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
-      <c r="D614" s="33"/>
+      <c r="D614" s="39"/>
       <c r="E614" s="3"/>
       <c r="F614" s="3"/>
       <c r="G614" s="3"/>
@@ -16246,7 +16270,7 @@
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
-      <c r="D615" s="33"/>
+      <c r="D615" s="39"/>
       <c r="E615" s="3"/>
       <c r="F615" s="3"/>
       <c r="G615" s="3"/>
@@ -16271,7 +16295,7 @@
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
-      <c r="D616" s="33"/>
+      <c r="D616" s="39"/>
       <c r="E616" s="3"/>
       <c r="F616" s="3"/>
       <c r="G616" s="3"/>
@@ -16296,7 +16320,7 @@
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
-      <c r="D617" s="33"/>
+      <c r="D617" s="39"/>
       <c r="E617" s="3"/>
       <c r="F617" s="3"/>
       <c r="G617" s="3"/>
@@ -16321,7 +16345,7 @@
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
-      <c r="D618" s="33"/>
+      <c r="D618" s="39"/>
       <c r="E618" s="3"/>
       <c r="F618" s="3"/>
       <c r="G618" s="3"/>
@@ -16346,7 +16370,7 @@
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
-      <c r="D619" s="33"/>
+      <c r="D619" s="39"/>
       <c r="E619" s="3"/>
       <c r="F619" s="3"/>
       <c r="G619" s="3"/>
@@ -16371,7 +16395,7 @@
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
-      <c r="D620" s="33"/>
+      <c r="D620" s="39"/>
       <c r="E620" s="3"/>
       <c r="F620" s="3"/>
       <c r="G620" s="3"/>
@@ -16396,7 +16420,7 @@
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
-      <c r="D621" s="33"/>
+      <c r="D621" s="39"/>
       <c r="E621" s="3"/>
       <c r="F621" s="3"/>
       <c r="G621" s="3"/>
@@ -16421,7 +16445,7 @@
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
-      <c r="D622" s="33"/>
+      <c r="D622" s="39"/>
       <c r="E622" s="3"/>
       <c r="F622" s="3"/>
       <c r="G622" s="3"/>
@@ -16446,7 +16470,7 @@
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
-      <c r="D623" s="33"/>
+      <c r="D623" s="39"/>
       <c r="E623" s="3"/>
       <c r="F623" s="3"/>
       <c r="G623" s="3"/>
@@ -16471,7 +16495,7 @@
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
-      <c r="D624" s="33"/>
+      <c r="D624" s="39"/>
       <c r="E624" s="3"/>
       <c r="F624" s="3"/>
       <c r="G624" s="3"/>
@@ -16496,7 +16520,7 @@
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
-      <c r="D625" s="33"/>
+      <c r="D625" s="39"/>
       <c r="E625" s="3"/>
       <c r="F625" s="3"/>
       <c r="G625" s="3"/>
@@ -16521,7 +16545,7 @@
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
-      <c r="D626" s="33"/>
+      <c r="D626" s="39"/>
       <c r="E626" s="3"/>
       <c r="F626" s="3"/>
       <c r="G626" s="3"/>
@@ -16546,7 +16570,7 @@
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
-      <c r="D627" s="33"/>
+      <c r="D627" s="39"/>
       <c r="E627" s="3"/>
       <c r="F627" s="3"/>
       <c r="G627" s="3"/>
@@ -16571,7 +16595,7 @@
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
-      <c r="D628" s="33"/>
+      <c r="D628" s="39"/>
       <c r="E628" s="3"/>
       <c r="F628" s="3"/>
       <c r="G628" s="3"/>
@@ -16596,7 +16620,7 @@
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
-      <c r="D629" s="33"/>
+      <c r="D629" s="39"/>
       <c r="E629" s="3"/>
       <c r="F629" s="3"/>
       <c r="G629" s="3"/>
@@ -16621,7 +16645,7 @@
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
-      <c r="D630" s="33"/>
+      <c r="D630" s="39"/>
       <c r="E630" s="3"/>
       <c r="F630" s="3"/>
       <c r="G630" s="3"/>
@@ -16646,7 +16670,7 @@
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
-      <c r="D631" s="33"/>
+      <c r="D631" s="39"/>
       <c r="E631" s="3"/>
       <c r="F631" s="3"/>
       <c r="G631" s="3"/>
@@ -16671,7 +16695,7 @@
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
-      <c r="D632" s="33"/>
+      <c r="D632" s="39"/>
       <c r="E632" s="3"/>
       <c r="F632" s="3"/>
       <c r="G632" s="3"/>
@@ -16696,7 +16720,7 @@
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
-      <c r="D633" s="33"/>
+      <c r="D633" s="39"/>
       <c r="E633" s="3"/>
       <c r="F633" s="3"/>
       <c r="G633" s="3"/>
@@ -16721,7 +16745,7 @@
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
-      <c r="D634" s="33"/>
+      <c r="D634" s="39"/>
       <c r="E634" s="3"/>
       <c r="F634" s="3"/>
       <c r="G634" s="3"/>
@@ -16746,7 +16770,7 @@
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
-      <c r="D635" s="33"/>
+      <c r="D635" s="39"/>
       <c r="E635" s="3"/>
       <c r="F635" s="3"/>
       <c r="G635" s="3"/>
@@ -16771,7 +16795,7 @@
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
-      <c r="D636" s="33"/>
+      <c r="D636" s="39"/>
       <c r="E636" s="3"/>
       <c r="F636" s="3"/>
       <c r="G636" s="3"/>
@@ -16796,7 +16820,7 @@
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
-      <c r="D637" s="33"/>
+      <c r="D637" s="39"/>
       <c r="E637" s="3"/>
       <c r="F637" s="3"/>
       <c r="G637" s="3"/>
@@ -16821,7 +16845,7 @@
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
-      <c r="D638" s="33"/>
+      <c r="D638" s="39"/>
       <c r="E638" s="3"/>
       <c r="F638" s="3"/>
       <c r="G638" s="3"/>
@@ -16846,7 +16870,7 @@
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
-      <c r="D639" s="33"/>
+      <c r="D639" s="39"/>
       <c r="E639" s="3"/>
       <c r="F639" s="3"/>
       <c r="G639" s="3"/>
@@ -16871,7 +16895,7 @@
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
-      <c r="D640" s="33"/>
+      <c r="D640" s="39"/>
       <c r="E640" s="3"/>
       <c r="F640" s="3"/>
       <c r="G640" s="3"/>
@@ -16896,7 +16920,7 @@
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
-      <c r="D641" s="33"/>
+      <c r="D641" s="39"/>
       <c r="E641" s="3"/>
       <c r="F641" s="3"/>
       <c r="G641" s="3"/>
@@ -16921,7 +16945,7 @@
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
-      <c r="D642" s="33"/>
+      <c r="D642" s="39"/>
       <c r="E642" s="3"/>
       <c r="F642" s="3"/>
       <c r="G642" s="3"/>
@@ -16946,7 +16970,7 @@
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
-      <c r="D643" s="33"/>
+      <c r="D643" s="39"/>
       <c r="E643" s="3"/>
       <c r="F643" s="3"/>
       <c r="G643" s="3"/>
@@ -16971,7 +16995,7 @@
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
-      <c r="D644" s="33"/>
+      <c r="D644" s="39"/>
       <c r="E644" s="3"/>
       <c r="F644" s="3"/>
       <c r="G644" s="3"/>
@@ -16996,7 +17020,7 @@
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
-      <c r="D645" s="33"/>
+      <c r="D645" s="39"/>
       <c r="E645" s="3"/>
       <c r="F645" s="3"/>
       <c r="G645" s="3"/>
@@ -17021,7 +17045,7 @@
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
-      <c r="D646" s="33"/>
+      <c r="D646" s="39"/>
       <c r="E646" s="3"/>
       <c r="F646" s="3"/>
       <c r="G646" s="3"/>
@@ -17046,7 +17070,7 @@
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
-      <c r="D647" s="33"/>
+      <c r="D647" s="39"/>
       <c r="E647" s="3"/>
       <c r="F647" s="3"/>
       <c r="G647" s="3"/>
@@ -17071,7 +17095,7 @@
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
-      <c r="D648" s="33"/>
+      <c r="D648" s="39"/>
       <c r="E648" s="3"/>
       <c r="F648" s="3"/>
       <c r="G648" s="3"/>
@@ -17096,7 +17120,7 @@
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
-      <c r="D649" s="33"/>
+      <c r="D649" s="39"/>
       <c r="E649" s="3"/>
       <c r="F649" s="3"/>
       <c r="G649" s="3"/>
@@ -17121,7 +17145,7 @@
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
-      <c r="D650" s="33"/>
+      <c r="D650" s="39"/>
       <c r="E650" s="3"/>
       <c r="F650" s="3"/>
       <c r="G650" s="3"/>
@@ -17146,7 +17170,7 @@
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
-      <c r="D651" s="33"/>
+      <c r="D651" s="39"/>
       <c r="E651" s="3"/>
       <c r="F651" s="3"/>
       <c r="G651" s="3"/>
@@ -17171,7 +17195,7 @@
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
-      <c r="D652" s="33"/>
+      <c r="D652" s="39"/>
       <c r="E652" s="3"/>
       <c r="F652" s="3"/>
       <c r="G652" s="3"/>
@@ -17196,7 +17220,7 @@
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
-      <c r="D653" s="33"/>
+      <c r="D653" s="39"/>
       <c r="E653" s="3"/>
       <c r="F653" s="3"/>
       <c r="G653" s="3"/>
@@ -17221,7 +17245,7 @@
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
-      <c r="D654" s="33"/>
+      <c r="D654" s="39"/>
       <c r="E654" s="3"/>
       <c r="F654" s="3"/>
       <c r="G654" s="3"/>
@@ -17246,7 +17270,7 @@
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
-      <c r="D655" s="33"/>
+      <c r="D655" s="39"/>
       <c r="E655" s="3"/>
       <c r="F655" s="3"/>
       <c r="G655" s="3"/>
@@ -17271,7 +17295,7 @@
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
-      <c r="D656" s="33"/>
+      <c r="D656" s="39"/>
       <c r="E656" s="3"/>
       <c r="F656" s="3"/>
       <c r="G656" s="3"/>
@@ -17296,7 +17320,7 @@
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
-      <c r="D657" s="33"/>
+      <c r="D657" s="39"/>
       <c r="E657" s="3"/>
       <c r="F657" s="3"/>
       <c r="G657" s="3"/>
@@ -17321,7 +17345,7 @@
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
-      <c r="D658" s="33"/>
+      <c r="D658" s="39"/>
       <c r="E658" s="3"/>
       <c r="F658" s="3"/>
       <c r="G658" s="3"/>
@@ -17346,7 +17370,7 @@
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
-      <c r="D659" s="33"/>
+      <c r="D659" s="39"/>
       <c r="E659" s="3"/>
       <c r="F659" s="3"/>
       <c r="G659" s="3"/>
@@ -17371,7 +17395,7 @@
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
-      <c r="D660" s="33"/>
+      <c r="D660" s="39"/>
       <c r="E660" s="3"/>
       <c r="F660" s="3"/>
       <c r="G660" s="3"/>
@@ -17396,7 +17420,7 @@
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
-      <c r="D661" s="33"/>
+      <c r="D661" s="39"/>
       <c r="E661" s="3"/>
       <c r="F661" s="3"/>
       <c r="G661" s="3"/>
@@ -17421,7 +17445,7 @@
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
-      <c r="D662" s="33"/>
+      <c r="D662" s="39"/>
       <c r="E662" s="3"/>
       <c r="F662" s="3"/>
       <c r="G662" s="3"/>
@@ -17446,7 +17470,7 @@
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
-      <c r="D663" s="33"/>
+      <c r="D663" s="39"/>
       <c r="E663" s="3"/>
       <c r="F663" s="3"/>
       <c r="G663" s="3"/>
@@ -17471,7 +17495,7 @@
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
-      <c r="D664" s="33"/>
+      <c r="D664" s="39"/>
       <c r="E664" s="3"/>
       <c r="F664" s="3"/>
       <c r="G664" s="3"/>
@@ -17496,7 +17520,7 @@
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
-      <c r="D665" s="33"/>
+      <c r="D665" s="39"/>
       <c r="E665" s="3"/>
       <c r="F665" s="3"/>
       <c r="G665" s="3"/>
@@ -17521,7 +17545,7 @@
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
-      <c r="D666" s="33"/>
+      <c r="D666" s="39"/>
       <c r="E666" s="3"/>
       <c r="F666" s="3"/>
       <c r="G666" s="3"/>
@@ -17546,7 +17570,7 @@
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
-      <c r="D667" s="33"/>
+      <c r="D667" s="39"/>
       <c r="E667" s="3"/>
       <c r="F667" s="3"/>
       <c r="G667" s="3"/>
@@ -17571,7 +17595,7 @@
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
-      <c r="D668" s="33"/>
+      <c r="D668" s="39"/>
       <c r="E668" s="3"/>
       <c r="F668" s="3"/>
       <c r="G668" s="3"/>
@@ -17596,7 +17620,7 @@
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
-      <c r="D669" s="33"/>
+      <c r="D669" s="39"/>
       <c r="E669" s="3"/>
       <c r="F669" s="3"/>
       <c r="G669" s="3"/>
@@ -17621,7 +17645,7 @@
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
-      <c r="D670" s="33"/>
+      <c r="D670" s="39"/>
       <c r="E670" s="3"/>
       <c r="F670" s="3"/>
       <c r="G670" s="3"/>
@@ -17646,7 +17670,7 @@
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
-      <c r="D671" s="33"/>
+      <c r="D671" s="39"/>
       <c r="E671" s="3"/>
       <c r="F671" s="3"/>
       <c r="G671" s="3"/>
@@ -17671,7 +17695,7 @@
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
-      <c r="D672" s="33"/>
+      <c r="D672" s="39"/>
       <c r="E672" s="3"/>
       <c r="F672" s="3"/>
       <c r="G672" s="3"/>
@@ -17696,7 +17720,7 @@
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
-      <c r="D673" s="33"/>
+      <c r="D673" s="39"/>
       <c r="E673" s="3"/>
       <c r="F673" s="3"/>
       <c r="G673" s="3"/>
@@ -17721,7 +17745,7 @@
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
-      <c r="D674" s="33"/>
+      <c r="D674" s="39"/>
       <c r="E674" s="3"/>
       <c r="F674" s="3"/>
       <c r="G674" s="3"/>
@@ -17746,7 +17770,7 @@
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
-      <c r="D675" s="33"/>
+      <c r="D675" s="39"/>
       <c r="E675" s="3"/>
       <c r="F675" s="3"/>
       <c r="G675" s="3"/>
@@ -17771,7 +17795,7 @@
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
-      <c r="D676" s="33"/>
+      <c r="D676" s="39"/>
       <c r="E676" s="3"/>
       <c r="F676" s="3"/>
       <c r="G676" s="3"/>
@@ -17796,7 +17820,7 @@
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
-      <c r="D677" s="33"/>
+      <c r="D677" s="39"/>
       <c r="E677" s="3"/>
       <c r="F677" s="3"/>
       <c r="G677" s="3"/>
@@ -17821,7 +17845,7 @@
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
-      <c r="D678" s="33"/>
+      <c r="D678" s="39"/>
       <c r="E678" s="3"/>
       <c r="F678" s="3"/>
       <c r="G678" s="3"/>
@@ -17846,7 +17870,7 @@
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
-      <c r="D679" s="33"/>
+      <c r="D679" s="39"/>
       <c r="E679" s="3"/>
       <c r="F679" s="3"/>
       <c r="G679" s="3"/>
@@ -17871,7 +17895,7 @@
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
-      <c r="D680" s="33"/>
+      <c r="D680" s="39"/>
       <c r="E680" s="3"/>
       <c r="F680" s="3"/>
       <c r="G680" s="3"/>
@@ -17896,7 +17920,7 @@
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
-      <c r="D681" s="33"/>
+      <c r="D681" s="39"/>
       <c r="E681" s="3"/>
       <c r="F681" s="3"/>
       <c r="G681" s="3"/>
@@ -17921,7 +17945,7 @@
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
-      <c r="D682" s="33"/>
+      <c r="D682" s="39"/>
       <c r="E682" s="3"/>
       <c r="F682" s="3"/>
       <c r="G682" s="3"/>
@@ -17946,7 +17970,7 @@
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
-      <c r="D683" s="33"/>
+      <c r="D683" s="39"/>
       <c r="E683" s="3"/>
       <c r="F683" s="3"/>
       <c r="G683" s="3"/>
@@ -17971,7 +17995,7 @@
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
-      <c r="D684" s="33"/>
+      <c r="D684" s="39"/>
       <c r="E684" s="3"/>
       <c r="F684" s="3"/>
       <c r="G684" s="3"/>
@@ -17996,7 +18020,7 @@
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
-      <c r="D685" s="33"/>
+      <c r="D685" s="39"/>
       <c r="E685" s="3"/>
       <c r="F685" s="3"/>
       <c r="G685" s="3"/>
@@ -18021,7 +18045,7 @@
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
-      <c r="D686" s="33"/>
+      <c r="D686" s="39"/>
       <c r="E686" s="3"/>
       <c r="F686" s="3"/>
       <c r="G686" s="3"/>
@@ -18046,7 +18070,7 @@
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
-      <c r="D687" s="33"/>
+      <c r="D687" s="39"/>
       <c r="E687" s="3"/>
       <c r="F687" s="3"/>
       <c r="G687" s="3"/>
@@ -18071,7 +18095,7 @@
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
-      <c r="D688" s="33"/>
+      <c r="D688" s="39"/>
       <c r="E688" s="3"/>
       <c r="F688" s="3"/>
       <c r="G688" s="3"/>
@@ -18096,7 +18120,7 @@
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
-      <c r="D689" s="33"/>
+      <c r="D689" s="39"/>
       <c r="E689" s="3"/>
       <c r="F689" s="3"/>
       <c r="G689" s="3"/>
@@ -18121,7 +18145,7 @@
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
-      <c r="D690" s="33"/>
+      <c r="D690" s="39"/>
       <c r="E690" s="3"/>
       <c r="F690" s="3"/>
       <c r="G690" s="3"/>
@@ -18146,7 +18170,7 @@
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
-      <c r="D691" s="33"/>
+      <c r="D691" s="39"/>
       <c r="E691" s="3"/>
       <c r="F691" s="3"/>
       <c r="G691" s="3"/>
@@ -18171,7 +18195,7 @@
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
-      <c r="D692" s="33"/>
+      <c r="D692" s="39"/>
       <c r="E692" s="3"/>
       <c r="F692" s="3"/>
       <c r="G692" s="3"/>
@@ -18196,7 +18220,7 @@
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
-      <c r="D693" s="33"/>
+      <c r="D693" s="39"/>
       <c r="E693" s="3"/>
       <c r="F693" s="3"/>
       <c r="G693" s="3"/>
@@ -18221,7 +18245,7 @@
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
-      <c r="D694" s="33"/>
+      <c r="D694" s="39"/>
       <c r="E694" s="3"/>
       <c r="F694" s="3"/>
       <c r="G694" s="3"/>
@@ -18246,7 +18270,7 @@
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
-      <c r="D695" s="33"/>
+      <c r="D695" s="39"/>
       <c r="E695" s="3"/>
       <c r="F695" s="3"/>
       <c r="G695" s="3"/>
@@ -18271,7 +18295,7 @@
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
-      <c r="D696" s="33"/>
+      <c r="D696" s="39"/>
       <c r="E696" s="3"/>
       <c r="F696" s="3"/>
       <c r="G696" s="3"/>
@@ -18296,7 +18320,7 @@
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
-      <c r="D697" s="33"/>
+      <c r="D697" s="39"/>
       <c r="E697" s="3"/>
       <c r="F697" s="3"/>
       <c r="G697" s="3"/>
@@ -18321,7 +18345,7 @@
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
-      <c r="D698" s="33"/>
+      <c r="D698" s="39"/>
       <c r="E698" s="3"/>
       <c r="F698" s="3"/>
       <c r="G698" s="3"/>
@@ -18346,7 +18370,7 @@
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
-      <c r="D699" s="33"/>
+      <c r="D699" s="39"/>
       <c r="E699" s="3"/>
       <c r="F699" s="3"/>
       <c r="G699" s="3"/>
@@ -18371,7 +18395,7 @@
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
-      <c r="D700" s="33"/>
+      <c r="D700" s="39"/>
       <c r="E700" s="3"/>
       <c r="F700" s="3"/>
       <c r="G700" s="3"/>
@@ -18396,7 +18420,7 @@
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
-      <c r="D701" s="33"/>
+      <c r="D701" s="39"/>
       <c r="E701" s="3"/>
       <c r="F701" s="3"/>
       <c r="G701" s="3"/>
@@ -18421,7 +18445,7 @@
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
-      <c r="D702" s="33"/>
+      <c r="D702" s="39"/>
       <c r="E702" s="3"/>
       <c r="F702" s="3"/>
       <c r="G702" s="3"/>
@@ -18446,7 +18470,7 @@
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
-      <c r="D703" s="33"/>
+      <c r="D703" s="39"/>
       <c r="E703" s="3"/>
       <c r="F703" s="3"/>
       <c r="G703" s="3"/>
@@ -18471,7 +18495,7 @@
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
-      <c r="D704" s="33"/>
+      <c r="D704" s="39"/>
       <c r="E704" s="3"/>
       <c r="F704" s="3"/>
       <c r="G704" s="3"/>
@@ -18496,7 +18520,7 @@
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
-      <c r="D705" s="33"/>
+      <c r="D705" s="39"/>
       <c r="E705" s="3"/>
       <c r="F705" s="3"/>
       <c r="G705" s="3"/>
@@ -18521,7 +18545,7 @@
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
-      <c r="D706" s="33"/>
+      <c r="D706" s="39"/>
       <c r="E706" s="3"/>
       <c r="F706" s="3"/>
       <c r="G706" s="3"/>
@@ -18546,7 +18570,7 @@
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
-      <c r="D707" s="33"/>
+      <c r="D707" s="39"/>
       <c r="E707" s="3"/>
       <c r="F707" s="3"/>
       <c r="G707" s="3"/>
@@ -18571,7 +18595,7 @@
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
-      <c r="D708" s="33"/>
+      <c r="D708" s="39"/>
       <c r="E708" s="3"/>
       <c r="F708" s="3"/>
       <c r="G708" s="3"/>
@@ -18596,7 +18620,7 @@
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
-      <c r="D709" s="33"/>
+      <c r="D709" s="39"/>
       <c r="E709" s="3"/>
       <c r="F709" s="3"/>
       <c r="G709" s="3"/>
@@ -18621,7 +18645,7 @@
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
-      <c r="D710" s="33"/>
+      <c r="D710" s="39"/>
       <c r="E710" s="3"/>
       <c r="F710" s="3"/>
       <c r="G710" s="3"/>
@@ -18646,7 +18670,7 @@
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
-      <c r="D711" s="33"/>
+      <c r="D711" s="39"/>
       <c r="E711" s="3"/>
       <c r="F711" s="3"/>
       <c r="G711" s="3"/>
@@ -18671,7 +18695,7 @@
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
-      <c r="D712" s="33"/>
+      <c r="D712" s="39"/>
       <c r="E712" s="3"/>
       <c r="F712" s="3"/>
       <c r="G712" s="3"/>
@@ -18696,7 +18720,7 @@
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
-      <c r="D713" s="33"/>
+      <c r="D713" s="39"/>
       <c r="E713" s="3"/>
       <c r="F713" s="3"/>
       <c r="G713" s="3"/>
@@ -18721,7 +18745,7 @@
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
-      <c r="D714" s="33"/>
+      <c r="D714" s="39"/>
       <c r="E714" s="3"/>
       <c r="F714" s="3"/>
       <c r="G714" s="3"/>
@@ -18746,7 +18770,7 @@
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
-      <c r="D715" s="33"/>
+      <c r="D715" s="39"/>
       <c r="E715" s="3"/>
       <c r="F715" s="3"/>
       <c r="G715" s="3"/>
@@ -18771,7 +18795,7 @@
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
-      <c r="D716" s="33"/>
+      <c r="D716" s="39"/>
       <c r="E716" s="3"/>
       <c r="F716" s="3"/>
       <c r="G716" s="3"/>
@@ -18796,7 +18820,7 @@
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
-      <c r="D717" s="33"/>
+      <c r="D717" s="39"/>
       <c r="E717" s="3"/>
       <c r="F717" s="3"/>
       <c r="G717" s="3"/>
@@ -18821,7 +18845,7 @@
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
-      <c r="D718" s="33"/>
+      <c r="D718" s="39"/>
       <c r="E718" s="3"/>
       <c r="F718" s="3"/>
       <c r="G718" s="3"/>
@@ -18846,7 +18870,7 @@
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
-      <c r="D719" s="33"/>
+      <c r="D719" s="39"/>
       <c r="E719" s="3"/>
       <c r="F719" s="3"/>
       <c r="G719" s="3"/>
@@ -18871,7 +18895,7 @@
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
-      <c r="D720" s="33"/>
+      <c r="D720" s="39"/>
       <c r="E720" s="3"/>
       <c r="F720" s="3"/>
       <c r="G720" s="3"/>
@@ -18896,7 +18920,7 @@
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
-      <c r="D721" s="33"/>
+      <c r="D721" s="39"/>
       <c r="E721" s="3"/>
       <c r="F721" s="3"/>
       <c r="G721" s="3"/>
@@ -18921,7 +18945,7 @@
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
-      <c r="D722" s="33"/>
+      <c r="D722" s="39"/>
       <c r="E722" s="3"/>
       <c r="F722" s="3"/>
       <c r="G722" s="3"/>
@@ -18946,7 +18970,7 @@
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
-      <c r="D723" s="33"/>
+      <c r="D723" s="39"/>
       <c r="E723" s="3"/>
       <c r="F723" s="3"/>
       <c r="G723" s="3"/>
@@ -18971,7 +18995,7 @@
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
-      <c r="D724" s="33"/>
+      <c r="D724" s="39"/>
       <c r="E724" s="3"/>
       <c r="F724" s="3"/>
       <c r="G724" s="3"/>
@@ -18996,7 +19020,7 @@
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
-      <c r="D725" s="33"/>
+      <c r="D725" s="39"/>
       <c r="E725" s="3"/>
       <c r="F725" s="3"/>
       <c r="G725" s="3"/>
@@ -19021,7 +19045,7 @@
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
-      <c r="D726" s="33"/>
+      <c r="D726" s="39"/>
       <c r="E726" s="3"/>
       <c r="F726" s="3"/>
       <c r="G726" s="3"/>
@@ -19046,7 +19070,7 @@
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
-      <c r="D727" s="33"/>
+      <c r="D727" s="39"/>
       <c r="E727" s="3"/>
       <c r="F727" s="3"/>
       <c r="G727" s="3"/>
@@ -19071,7 +19095,7 @@
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
-      <c r="D728" s="33"/>
+      <c r="D728" s="39"/>
       <c r="E728" s="3"/>
       <c r="F728" s="3"/>
       <c r="G728" s="3"/>
@@ -19096,7 +19120,7 @@
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
-      <c r="D729" s="33"/>
+      <c r="D729" s="39"/>
       <c r="E729" s="3"/>
       <c r="F729" s="3"/>
       <c r="G729" s="3"/>
@@ -19121,7 +19145,7 @@
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
-      <c r="D730" s="33"/>
+      <c r="D730" s="39"/>
       <c r="E730" s="3"/>
       <c r="F730" s="3"/>
       <c r="G730" s="3"/>
@@ -19146,7 +19170,7 @@
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
-      <c r="D731" s="33"/>
+      <c r="D731" s="39"/>
       <c r="E731" s="3"/>
       <c r="F731" s="3"/>
       <c r="G731" s="3"/>
@@ -19171,7 +19195,7 @@
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
-      <c r="D732" s="33"/>
+      <c r="D732" s="39"/>
       <c r="E732" s="3"/>
       <c r="F732" s="3"/>
       <c r="G732" s="3"/>
@@ -19196,7 +19220,7 @@
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
-      <c r="D733" s="33"/>
+      <c r="D733" s="39"/>
       <c r="E733" s="3"/>
       <c r="F733" s="3"/>
       <c r="G733" s="3"/>
@@ -19221,7 +19245,7 @@
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
-      <c r="D734" s="33"/>
+      <c r="D734" s="39"/>
       <c r="E734" s="3"/>
       <c r="F734" s="3"/>
       <c r="G734" s="3"/>
@@ -19246,7 +19270,7 @@
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
-      <c r="D735" s="33"/>
+      <c r="D735" s="39"/>
       <c r="E735" s="3"/>
       <c r="F735" s="3"/>
       <c r="G735" s="3"/>
@@ -19271,7 +19295,7 @@
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
-      <c r="D736" s="33"/>
+      <c r="D736" s="39"/>
       <c r="E736" s="3"/>
       <c r="F736" s="3"/>
       <c r="G736" s="3"/>
@@ -19296,7 +19320,7 @@
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
-      <c r="D737" s="33"/>
+      <c r="D737" s="39"/>
       <c r="E737" s="3"/>
       <c r="F737" s="3"/>
       <c r="G737" s="3"/>
@@ -19321,7 +19345,7 @@
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
-      <c r="D738" s="33"/>
+      <c r="D738" s="39"/>
       <c r="E738" s="3"/>
       <c r="F738" s="3"/>
       <c r="G738" s="3"/>
@@ -19346,7 +19370,7 @@
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
-      <c r="D739" s="33"/>
+      <c r="D739" s="39"/>
       <c r="E739" s="3"/>
       <c r="F739" s="3"/>
       <c r="G739" s="3"/>
@@ -19371,7 +19395,7 @@
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
-      <c r="D740" s="33"/>
+      <c r="D740" s="39"/>
       <c r="E740" s="3"/>
       <c r="F740" s="3"/>
       <c r="G740" s="3"/>
@@ -19396,7 +19420,7 @@
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
-      <c r="D741" s="33"/>
+      <c r="D741" s="39"/>
       <c r="E741" s="3"/>
       <c r="F741" s="3"/>
       <c r="G741" s="3"/>
@@ -19421,7 +19445,7 @@
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
-      <c r="D742" s="33"/>
+      <c r="D742" s="39"/>
       <c r="E742" s="3"/>
       <c r="F742" s="3"/>
       <c r="G742" s="3"/>
@@ -19446,7 +19470,7 @@
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
-      <c r="D743" s="33"/>
+      <c r="D743" s="39"/>
       <c r="E743" s="3"/>
       <c r="F743" s="3"/>
       <c r="G743" s="3"/>
@@ -19471,7 +19495,7 @@
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
-      <c r="D744" s="33"/>
+      <c r="D744" s="39"/>
       <c r="E744" s="3"/>
       <c r="F744" s="3"/>
       <c r="G744" s="3"/>
@@ -19496,7 +19520,7 @@
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
-      <c r="D745" s="33"/>
+      <c r="D745" s="39"/>
       <c r="E745" s="3"/>
       <c r="F745" s="3"/>
       <c r="G745" s="3"/>
@@ -19521,7 +19545,7 @@
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
-      <c r="D746" s="33"/>
+      <c r="D746" s="39"/>
       <c r="E746" s="3"/>
       <c r="F746" s="3"/>
       <c r="G746" s="3"/>
@@ -19546,7 +19570,7 @@
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
-      <c r="D747" s="33"/>
+      <c r="D747" s="39"/>
       <c r="E747" s="3"/>
       <c r="F747" s="3"/>
       <c r="G747" s="3"/>
@@ -19571,7 +19595,7 @@
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
-      <c r="D748" s="33"/>
+      <c r="D748" s="39"/>
       <c r="E748" s="3"/>
       <c r="F748" s="3"/>
       <c r="G748" s="3"/>
@@ -19596,7 +19620,7 @@
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
-      <c r="D749" s="33"/>
+      <c r="D749" s="39"/>
       <c r="E749" s="3"/>
       <c r="F749" s="3"/>
       <c r="G749" s="3"/>
@@ -19621,7 +19645,7 @@
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
-      <c r="D750" s="33"/>
+      <c r="D750" s="39"/>
       <c r="E750" s="3"/>
       <c r="F750" s="3"/>
       <c r="G750" s="3"/>
@@ -19646,7 +19670,7 @@
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
-      <c r="D751" s="33"/>
+      <c r="D751" s="39"/>
       <c r="E751" s="3"/>
       <c r="F751" s="3"/>
       <c r="G751" s="3"/>
@@ -19671,7 +19695,7 @@
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
-      <c r="D752" s="33"/>
+      <c r="D752" s="39"/>
       <c r="E752" s="3"/>
       <c r="F752" s="3"/>
       <c r="G752" s="3"/>
@@ -19696,7 +19720,7 @@
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
-      <c r="D753" s="33"/>
+      <c r="D753" s="39"/>
       <c r="E753" s="3"/>
       <c r="F753" s="3"/>
       <c r="G753" s="3"/>
@@ -19721,7 +19745,7 @@
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
-      <c r="D754" s="33"/>
+      <c r="D754" s="39"/>
       <c r="E754" s="3"/>
       <c r="F754" s="3"/>
       <c r="G754" s="3"/>
@@ -19746,7 +19770,7 @@
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
-      <c r="D755" s="33"/>
+      <c r="D755" s="39"/>
       <c r="E755" s="3"/>
       <c r="F755" s="3"/>
       <c r="G755" s="3"/>
@@ -19771,7 +19795,7 @@
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
-      <c r="D756" s="33"/>
+      <c r="D756" s="39"/>
       <c r="E756" s="3"/>
       <c r="F756" s="3"/>
       <c r="G756" s="3"/>
@@ -19796,7 +19820,7 @@
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
-      <c r="D757" s="33"/>
+      <c r="D757" s="39"/>
       <c r="E757" s="3"/>
       <c r="F757" s="3"/>
       <c r="G757" s="3"/>
@@ -19821,7 +19845,7 @@
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
-      <c r="D758" s="33"/>
+      <c r="D758" s="39"/>
       <c r="E758" s="3"/>
       <c r="F758" s="3"/>
       <c r="G758" s="3"/>
@@ -19846,7 +19870,7 @@
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
-      <c r="D759" s="33"/>
+      <c r="D759" s="39"/>
       <c r="E759" s="3"/>
       <c r="F759" s="3"/>
       <c r="G759" s="3"/>
@@ -19871,7 +19895,7 @@
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
-      <c r="D760" s="33"/>
+      <c r="D760" s="39"/>
       <c r="E760" s="3"/>
       <c r="F760" s="3"/>
       <c r="G760" s="3"/>
@@ -19896,7 +19920,7 @@
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
-      <c r="D761" s="33"/>
+      <c r="D761" s="39"/>
       <c r="E761" s="3"/>
       <c r="F761" s="3"/>
       <c r="G761" s="3"/>
@@ -19921,7 +19945,7 @@
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
-      <c r="D762" s="33"/>
+      <c r="D762" s="39"/>
       <c r="E762" s="3"/>
       <c r="F762" s="3"/>
       <c r="G762" s="3"/>
@@ -19946,7 +19970,7 @@
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
-      <c r="D763" s="33"/>
+      <c r="D763" s="39"/>
       <c r="E763" s="3"/>
       <c r="F763" s="3"/>
       <c r="G763" s="3"/>
@@ -19971,7 +19995,7 @@
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
-      <c r="D764" s="33"/>
+      <c r="D764" s="39"/>
       <c r="E764" s="3"/>
       <c r="F764" s="3"/>
       <c r="G764" s="3"/>
@@ -19996,7 +20020,7 @@
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
-      <c r="D765" s="33"/>
+      <c r="D765" s="39"/>
       <c r="E765" s="3"/>
       <c r="F765" s="3"/>
       <c r="G765" s="3"/>
@@ -20021,7 +20045,7 @@
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
-      <c r="D766" s="33"/>
+      <c r="D766" s="39"/>
       <c r="E766" s="3"/>
       <c r="F766" s="3"/>
       <c r="G766" s="3"/>
@@ -20046,7 +20070,7 @@
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
-      <c r="D767" s="33"/>
+      <c r="D767" s="39"/>
       <c r="E767" s="3"/>
       <c r="F767" s="3"/>
       <c r="G767" s="3"/>
@@ -20071,7 +20095,7 @@
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
-      <c r="D768" s="33"/>
+      <c r="D768" s="39"/>
       <c r="E768" s="3"/>
       <c r="F768" s="3"/>
       <c r="G768" s="3"/>
@@ -20096,7 +20120,7 @@
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
-      <c r="D769" s="33"/>
+      <c r="D769" s="39"/>
       <c r="E769" s="3"/>
       <c r="F769" s="3"/>
       <c r="G769" s="3"/>
@@ -20121,7 +20145,7 @@
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
-      <c r="D770" s="33"/>
+      <c r="D770" s="39"/>
       <c r="E770" s="3"/>
       <c r="F770" s="3"/>
       <c r="G770" s="3"/>
@@ -20146,7 +20170,7 @@
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
-      <c r="D771" s="33"/>
+      <c r="D771" s="39"/>
       <c r="E771" s="3"/>
       <c r="F771" s="3"/>
       <c r="G771" s="3"/>
@@ -20171,7 +20195,7 @@
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
-      <c r="D772" s="33"/>
+      <c r="D772" s="39"/>
       <c r="E772" s="3"/>
       <c r="F772" s="3"/>
       <c r="G772" s="3"/>
@@ -20196,7 +20220,7 @@
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
-      <c r="D773" s="33"/>
+      <c r="D773" s="39"/>
       <c r="E773" s="3"/>
       <c r="F773" s="3"/>
       <c r="G773" s="3"/>
@@ -20221,7 +20245,7 @@
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
-      <c r="D774" s="33"/>
+      <c r="D774" s="39"/>
       <c r="E774" s="3"/>
       <c r="F774" s="3"/>
       <c r="G774" s="3"/>
@@ -20246,7 +20270,7 @@
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
-      <c r="D775" s="33"/>
+      <c r="D775" s="39"/>
       <c r="E775" s="3"/>
       <c r="F775" s="3"/>
       <c r="G775" s="3"/>
@@ -20271,7 +20295,7 @@
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
-      <c r="D776" s="33"/>
+      <c r="D776" s="39"/>
       <c r="E776" s="3"/>
       <c r="F776" s="3"/>
       <c r="G776" s="3"/>
@@ -20296,7 +20320,7 @@
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
-      <c r="D777" s="33"/>
+      <c r="D777" s="39"/>
       <c r="E777" s="3"/>
       <c r="F777" s="3"/>
       <c r="G777" s="3"/>
@@ -20321,7 +20345,7 @@
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
-      <c r="D778" s="33"/>
+      <c r="D778" s="39"/>
       <c r="E778" s="3"/>
       <c r="F778" s="3"/>
       <c r="G778" s="3"/>
@@ -20346,7 +20370,7 @@
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
-      <c r="D779" s="33"/>
+      <c r="D779" s="39"/>
       <c r="E779" s="3"/>
       <c r="F779" s="3"/>
       <c r="G779" s="3"/>
@@ -20371,7 +20395,7 @@
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
-      <c r="D780" s="33"/>
+      <c r="D780" s="39"/>
       <c r="E780" s="3"/>
       <c r="F780" s="3"/>
       <c r="G780" s="3"/>
@@ -20396,7 +20420,7 @@
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
-      <c r="D781" s="33"/>
+      <c r="D781" s="39"/>
       <c r="E781" s="3"/>
       <c r="F781" s="3"/>
       <c r="G781" s="3"/>
@@ -20421,7 +20445,7 @@
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
-      <c r="D782" s="33"/>
+      <c r="D782" s="39"/>
       <c r="E782" s="3"/>
       <c r="F782" s="3"/>
       <c r="G782" s="3"/>
@@ -20446,7 +20470,7 @@
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
-      <c r="D783" s="33"/>
+      <c r="D783" s="39"/>
       <c r="E783" s="3"/>
       <c r="F783" s="3"/>
       <c r="G783" s="3"/>
@@ -20471,7 +20495,7 @@
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
-      <c r="D784" s="33"/>
+      <c r="D784" s="39"/>
       <c r="E784" s="3"/>
       <c r="F784" s="3"/>
       <c r="G784" s="3"/>
@@ -20496,7 +20520,7 @@
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
-      <c r="D785" s="33"/>
+      <c r="D785" s="39"/>
       <c r="E785" s="3"/>
       <c r="F785" s="3"/>
       <c r="G785" s="3"/>
@@ -20521,7 +20545,7 @@
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
-      <c r="D786" s="33"/>
+      <c r="D786" s="39"/>
       <c r="E786" s="3"/>
       <c r="F786" s="3"/>
       <c r="G786" s="3"/>
@@ -20546,7 +20570,7 @@
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
-      <c r="D787" s="33"/>
+      <c r="D787" s="39"/>
       <c r="E787" s="3"/>
       <c r="F787" s="3"/>
       <c r="G787" s="3"/>
@@ -20571,7 +20595,7 @@
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
-      <c r="D788" s="33"/>
+      <c r="D788" s="39"/>
       <c r="E788" s="3"/>
       <c r="F788" s="3"/>
       <c r="G788" s="3"/>
@@ -20596,7 +20620,7 @@
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
-      <c r="D789" s="33"/>
+      <c r="D789" s="39"/>
       <c r="E789" s="3"/>
       <c r="F789" s="3"/>
       <c r="G789" s="3"/>
@@ -20621,7 +20645,7 @@
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
-      <c r="D790" s="33"/>
+      <c r="D790" s="39"/>
       <c r="E790" s="3"/>
       <c r="F790" s="3"/>
       <c r="G790" s="3"/>
@@ -20646,7 +20670,7 @@
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
-      <c r="D791" s="33"/>
+      <c r="D791" s="39"/>
       <c r="E791" s="3"/>
       <c r="F791" s="3"/>
       <c r="G791" s="3"/>
@@ -20671,7 +20695,7 @@
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
-      <c r="D792" s="33"/>
+      <c r="D792" s="39"/>
       <c r="E792" s="3"/>
       <c r="F792" s="3"/>
       <c r="G792" s="3"/>
@@ -20696,7 +20720,7 @@
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
-      <c r="D793" s="33"/>
+      <c r="D793" s="39"/>
       <c r="E793" s="3"/>
       <c r="F793" s="3"/>
       <c r="G793" s="3"/>
@@ -20721,7 +20745,7 @@
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
-      <c r="D794" s="33"/>
+      <c r="D794" s="39"/>
       <c r="E794" s="3"/>
       <c r="F794" s="3"/>
       <c r="G794" s="3"/>
@@ -20746,7 +20770,7 @@
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
-      <c r="D795" s="33"/>
+      <c r="D795" s="39"/>
       <c r="E795" s="3"/>
       <c r="F795" s="3"/>
       <c r="G795" s="3"/>
@@ -20771,7 +20795,7 @@
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
-      <c r="D796" s="33"/>
+      <c r="D796" s="39"/>
       <c r="E796" s="3"/>
       <c r="F796" s="3"/>
       <c r="G796" s="3"/>
@@ -20796,7 +20820,7 @@
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
-      <c r="D797" s="33"/>
+      <c r="D797" s="39"/>
       <c r="E797" s="3"/>
       <c r="F797" s="3"/>
       <c r="G797" s="3"/>
@@ -20821,7 +20845,7 @@
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
-      <c r="D798" s="33"/>
+      <c r="D798" s="39"/>
       <c r="E798" s="3"/>
       <c r="F798" s="3"/>
       <c r="G798" s="3"/>
@@ -20846,7 +20870,7 @@
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
-      <c r="D799" s="33"/>
+      <c r="D799" s="39"/>
       <c r="E799" s="3"/>
       <c r="F799" s="3"/>
       <c r="G799" s="3"/>
@@ -20871,7 +20895,7 @@
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
-      <c r="D800" s="33"/>
+      <c r="D800" s="39"/>
       <c r="E800" s="3"/>
       <c r="F800" s="3"/>
       <c r="G800" s="3"/>
@@ -20896,7 +20920,7 @@
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
-      <c r="D801" s="33"/>
+      <c r="D801" s="39"/>
       <c r="E801" s="3"/>
       <c r="F801" s="3"/>
       <c r="G801" s="3"/>
@@ -20921,7 +20945,7 @@
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
-      <c r="D802" s="33"/>
+      <c r="D802" s="39"/>
       <c r="E802" s="3"/>
       <c r="F802" s="3"/>
       <c r="G802" s="3"/>
@@ -20946,7 +20970,7 @@
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
-      <c r="D803" s="33"/>
+      <c r="D803" s="39"/>
       <c r="E803" s="3"/>
       <c r="F803" s="3"/>
       <c r="G803" s="3"/>
@@ -20971,7 +20995,7 @@
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
-      <c r="D804" s="33"/>
+      <c r="D804" s="39"/>
       <c r="E804" s="3"/>
       <c r="F804" s="3"/>
       <c r="G804" s="3"/>
@@ -20996,7 +21020,7 @@
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
-      <c r="D805" s="33"/>
+      <c r="D805" s="39"/>
       <c r="E805" s="3"/>
       <c r="F805" s="3"/>
       <c r="G805" s="3"/>
@@ -21021,7 +21045,7 @@
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
-      <c r="D806" s="33"/>
+      <c r="D806" s="39"/>
       <c r="E806" s="3"/>
       <c r="F806" s="3"/>
       <c r="G806" s="3"/>
@@ -21046,7 +21070,7 @@
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
-      <c r="D807" s="33"/>
+      <c r="D807" s="39"/>
       <c r="E807" s="3"/>
       <c r="F807" s="3"/>
       <c r="G807" s="3"/>
@@ -21071,7 +21095,7 @@
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
-      <c r="D808" s="33"/>
+      <c r="D808" s="39"/>
       <c r="E808" s="3"/>
       <c r="F808" s="3"/>
       <c r="G808" s="3"/>
@@ -21096,7 +21120,7 @@
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
-      <c r="D809" s="33"/>
+      <c r="D809" s="39"/>
       <c r="E809" s="3"/>
       <c r="F809" s="3"/>
       <c r="G809" s="3"/>
@@ -21121,7 +21145,7 @@
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
-      <c r="D810" s="33"/>
+      <c r="D810" s="39"/>
       <c r="E810" s="3"/>
       <c r="F810" s="3"/>
       <c r="G810" s="3"/>
@@ -21146,7 +21170,7 @@
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
-      <c r="D811" s="33"/>
+      <c r="D811" s="39"/>
       <c r="E811" s="3"/>
       <c r="F811" s="3"/>
       <c r="G811" s="3"/>
@@ -21171,7 +21195,7 @@
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
-      <c r="D812" s="33"/>
+      <c r="D812" s="39"/>
       <c r="E812" s="3"/>
       <c r="F812" s="3"/>
       <c r="G812" s="3"/>
@@ -21196,7 +21220,7 @@
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
-      <c r="D813" s="33"/>
+      <c r="D813" s="39"/>
       <c r="E813" s="3"/>
       <c r="F813" s="3"/>
       <c r="G813" s="3"/>
@@ -21221,7 +21245,7 @@
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
-      <c r="D814" s="33"/>
+      <c r="D814" s="39"/>
       <c r="E814" s="3"/>
       <c r="F814" s="3"/>
       <c r="G814" s="3"/>
@@ -21246,7 +21270,7 @@
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
-      <c r="D815" s="33"/>
+      <c r="D815" s="39"/>
       <c r="E815" s="3"/>
       <c r="F815" s="3"/>
       <c r="G815" s="3"/>
@@ -21271,7 +21295,7 @@
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
-      <c r="D816" s="33"/>
+      <c r="D816" s="39"/>
       <c r="E816" s="3"/>
       <c r="F816" s="3"/>
       <c r="G816" s="3"/>
@@ -21296,7 +21320,7 @@
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
-      <c r="D817" s="33"/>
+      <c r="D817" s="39"/>
       <c r="E817" s="3"/>
       <c r="F817" s="3"/>
       <c r="G817" s="3"/>
@@ -21321,7 +21345,7 @@
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
-      <c r="D818" s="33"/>
+      <c r="D818" s="39"/>
       <c r="E818" s="3"/>
       <c r="F818" s="3"/>
       <c r="G818" s="3"/>
@@ -21346,7 +21370,7 @@
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
-      <c r="D819" s="33"/>
+      <c r="D819" s="39"/>
       <c r="E819" s="3"/>
       <c r="F819" s="3"/>
       <c r="G819" s="3"/>
@@ -21371,7 +21395,7 @@
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
-      <c r="D820" s="33"/>
+      <c r="D820" s="39"/>
       <c r="E820" s="3"/>
       <c r="F820" s="3"/>
       <c r="G820" s="3"/>
@@ -21396,7 +21420,7 @@
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
-      <c r="D821" s="33"/>
+      <c r="D821" s="39"/>
       <c r="E821" s="3"/>
       <c r="F821" s="3"/>
       <c r="G821" s="3"/>
@@ -21421,7 +21445,7 @@
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
-      <c r="D822" s="33"/>
+      <c r="D822" s="39"/>
       <c r="E822" s="3"/>
       <c r="F822" s="3"/>
       <c r="G822" s="3"/>
@@ -21446,7 +21470,7 @@
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
-      <c r="D823" s="33"/>
+      <c r="D823" s="39"/>
       <c r="E823" s="3"/>
       <c r="F823" s="3"/>
       <c r="G823" s="3"/>
@@ -21471,7 +21495,7 @@
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
-      <c r="D824" s="33"/>
+      <c r="D824" s="39"/>
       <c r="E824" s="3"/>
       <c r="F824" s="3"/>
       <c r="G824" s="3"/>
@@ -21496,7 +21520,7 @@
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
-      <c r="D825" s="33"/>
+      <c r="D825" s="39"/>
       <c r="E825" s="3"/>
       <c r="F825" s="3"/>
       <c r="G825" s="3"/>
@@ -21521,7 +21545,7 @@
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
-      <c r="D826" s="33"/>
+      <c r="D826" s="39"/>
       <c r="E826" s="3"/>
       <c r="F826" s="3"/>
       <c r="G826" s="3"/>
@@ -21546,7 +21570,7 @@
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
-      <c r="D827" s="33"/>
+      <c r="D827" s="39"/>
       <c r="E827" s="3"/>
       <c r="F827" s="3"/>
       <c r="G827" s="3"/>
@@ -21571,7 +21595,7 @@
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
-      <c r="D828" s="33"/>
+      <c r="D828" s="39"/>
       <c r="E828" s="3"/>
       <c r="F828" s="3"/>
       <c r="G828" s="3"/>
@@ -21596,7 +21620,7 @@
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
-      <c r="D829" s="33"/>
+      <c r="D829" s="39"/>
       <c r="E829" s="3"/>
       <c r="F829" s="3"/>
       <c r="G829" s="3"/>
@@ -21621,7 +21645,7 @@
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
-      <c r="D830" s="33"/>
+      <c r="D830" s="39"/>
       <c r="E830" s="3"/>
       <c r="F830" s="3"/>
       <c r="G830" s="3"/>
@@ -21646,7 +21670,7 @@
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
-      <c r="D831" s="33"/>
+      <c r="D831" s="39"/>
       <c r="E831" s="3"/>
       <c r="F831" s="3"/>
       <c r="G831" s="3"/>
@@ -21671,7 +21695,7 @@
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
-      <c r="D832" s="33"/>
+      <c r="D832" s="39"/>
       <c r="E832" s="3"/>
       <c r="F832" s="3"/>
       <c r="G832" s="3"/>
@@ -21696,7 +21720,7 @@
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
-      <c r="D833" s="33"/>
+      <c r="D833" s="39"/>
       <c r="E833" s="3"/>
       <c r="F833" s="3"/>
       <c r="G833" s="3"/>
@@ -21721,7 +21745,7 @@
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
-      <c r="D834" s="33"/>
+      <c r="D834" s="39"/>
       <c r="E834" s="3"/>
       <c r="F834" s="3"/>
       <c r="G834" s="3"/>
@@ -21746,7 +21770,7 @@
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
-      <c r="D835" s="33"/>
+      <c r="D835" s="39"/>
       <c r="E835" s="3"/>
       <c r="F835" s="3"/>
       <c r="G835" s="3"/>
@@ -21771,7 +21795,7 @@
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
-      <c r="D836" s="33"/>
+      <c r="D836" s="39"/>
       <c r="E836" s="3"/>
       <c r="F836" s="3"/>
       <c r="G836" s="3"/>
@@ -21796,7 +21820,7 @@
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
-      <c r="D837" s="33"/>
+      <c r="D837" s="39"/>
       <c r="E837" s="3"/>
       <c r="F837" s="3"/>
       <c r="G837" s="3"/>
@@ -21821,7 +21845,7 @@
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
-      <c r="D838" s="33"/>
+      <c r="D838" s="39"/>
       <c r="E838" s="3"/>
       <c r="F838" s="3"/>
       <c r="G838" s="3"/>
@@ -21846,7 +21870,7 @@
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
-      <c r="D839" s="33"/>
+      <c r="D839" s="39"/>
       <c r="E839" s="3"/>
       <c r="F839" s="3"/>
       <c r="G839" s="3"/>
@@ -21871,7 +21895,7 @@
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
-      <c r="D840" s="33"/>
+      <c r="D840" s="39"/>
       <c r="E840" s="3"/>
       <c r="F840" s="3"/>
       <c r="G840" s="3"/>
@@ -21896,7 +21920,7 @@
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
-      <c r="D841" s="33"/>
+      <c r="D841" s="39"/>
       <c r="E841" s="3"/>
       <c r="F841" s="3"/>
       <c r="G841" s="3"/>
@@ -21921,7 +21945,7 @@
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
-      <c r="D842" s="33"/>
+      <c r="D842" s="39"/>
       <c r="E842" s="3"/>
       <c r="F842" s="3"/>
       <c r="G842" s="3"/>
@@ -21946,7 +21970,7 @@
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
-      <c r="D843" s="33"/>
+      <c r="D843" s="39"/>
       <c r="E843" s="3"/>
       <c r="F843" s="3"/>
       <c r="G843" s="3"/>
@@ -21971,7 +21995,7 @@
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
-      <c r="D844" s="33"/>
+      <c r="D844" s="39"/>
       <c r="E844" s="3"/>
       <c r="F844" s="3"/>
       <c r="G844" s="3"/>
@@ -21996,7 +22020,7 @@
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
-      <c r="D845" s="33"/>
+      <c r="D845" s="39"/>
       <c r="E845" s="3"/>
       <c r="F845" s="3"/>
       <c r="G845" s="3"/>
@@ -22021,7 +22045,7 @@
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
-      <c r="D846" s="33"/>
+      <c r="D846" s="39"/>
       <c r="E846" s="3"/>
       <c r="F846" s="3"/>
       <c r="G846" s="3"/>
@@ -22046,7 +22070,7 @@
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
-      <c r="D847" s="33"/>
+      <c r="D847" s="39"/>
       <c r="E847" s="3"/>
       <c r="F847" s="3"/>
       <c r="G847" s="3"/>
@@ -22071,7 +22095,7 @@
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
-      <c r="D848" s="33"/>
+      <c r="D848" s="39"/>
       <c r="E848" s="3"/>
       <c r="F848" s="3"/>
       <c r="G848" s="3"/>
@@ -22096,7 +22120,7 @@
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
-      <c r="D849" s="33"/>
+      <c r="D849" s="39"/>
       <c r="E849" s="3"/>
       <c r="F849" s="3"/>
       <c r="G849" s="3"/>
@@ -22121,7 +22145,7 @@
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
-      <c r="D850" s="33"/>
+      <c r="D850" s="39"/>
       <c r="E850" s="3"/>
       <c r="F850" s="3"/>
       <c r="G850" s="3"/>
@@ -22146,7 +22170,7 @@
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
-      <c r="D851" s="33"/>
+      <c r="D851" s="39"/>
       <c r="E851" s="3"/>
       <c r="F851" s="3"/>
       <c r="G851" s="3"/>
@@ -22171,7 +22195,7 @@
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
-      <c r="D852" s="33"/>
+      <c r="D852" s="39"/>
       <c r="E852" s="3"/>
       <c r="F852" s="3"/>
       <c r="G852" s="3"/>
@@ -22196,7 +22220,7 @@
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
-      <c r="D853" s="33"/>
+      <c r="D853" s="39"/>
       <c r="E853" s="3"/>
       <c r="F853" s="3"/>
       <c r="G853" s="3"/>
@@ -22221,7 +22245,7 @@
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
-      <c r="D854" s="33"/>
+      <c r="D854" s="39"/>
       <c r="E854" s="3"/>
       <c r="F854" s="3"/>
       <c r="G854" s="3"/>
@@ -22246,7 +22270,7 @@
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
-      <c r="D855" s="33"/>
+      <c r="D855" s="39"/>
       <c r="E855" s="3"/>
       <c r="F855" s="3"/>
       <c r="G855" s="3"/>
@@ -22271,7 +22295,7 @@
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
-      <c r="D856" s="33"/>
+      <c r="D856" s="39"/>
       <c r="E856" s="3"/>
       <c r="F856" s="3"/>
       <c r="G856" s="3"/>
@@ -22296,7 +22320,7 @@
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
-      <c r="D857" s="33"/>
+      <c r="D857" s="39"/>
       <c r="E857" s="3"/>
       <c r="F857" s="3"/>
       <c r="G857" s="3"/>
@@ -22321,7 +22345,7 @@
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
-      <c r="D858" s="33"/>
+      <c r="D858" s="39"/>
       <c r="E858" s="3"/>
       <c r="F858" s="3"/>
       <c r="G858" s="3"/>
@@ -22346,7 +22370,7 @@
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
-      <c r="D859" s="33"/>
+      <c r="D859" s="39"/>
       <c r="E859" s="3"/>
       <c r="F859" s="3"/>
       <c r="G859" s="3"/>
@@ -22371,7 +22395,7 @@
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
-      <c r="D860" s="33"/>
+      <c r="D860" s="39"/>
       <c r="E860" s="3"/>
       <c r="F860" s="3"/>
       <c r="G860" s="3"/>
@@ -22396,7 +22420,7 @@
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
-      <c r="D861" s="33"/>
+      <c r="D861" s="39"/>
       <c r="E861" s="3"/>
       <c r="F861" s="3"/>
       <c r="G861" s="3"/>
@@ -22421,7 +22445,7 @@
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
-      <c r="D862" s="33"/>
+      <c r="D862" s="39"/>
       <c r="E862" s="3"/>
       <c r="F862" s="3"/>
       <c r="G862" s="3"/>
@@ -22446,7 +22470,7 @@
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
-      <c r="D863" s="33"/>
+      <c r="D863" s="39"/>
       <c r="E863" s="3"/>
       <c r="F863" s="3"/>
       <c r="G863" s="3"/>
@@ -22471,7 +22495,7 @@
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
-      <c r="D864" s="33"/>
+      <c r="D864" s="39"/>
       <c r="E864" s="3"/>
       <c r="F864" s="3"/>
       <c r="G864" s="3"/>
@@ -22496,7 +22520,7 @@
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
-      <c r="D865" s="33"/>
+      <c r="D865" s="39"/>
       <c r="E865" s="3"/>
       <c r="F865" s="3"/>
       <c r="G865" s="3"/>
@@ -22521,7 +22545,7 @@
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
-      <c r="D866" s="33"/>
+      <c r="D866" s="39"/>
       <c r="E866" s="3"/>
       <c r="F866" s="3"/>
       <c r="G866" s="3"/>
@@ -22546,7 +22570,7 @@
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
-      <c r="D867" s="33"/>
+      <c r="D867" s="39"/>
       <c r="E867" s="3"/>
       <c r="F867" s="3"/>
       <c r="G867" s="3"/>
@@ -22571,7 +22595,7 @@
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
-      <c r="D868" s="33"/>
+      <c r="D868" s="39"/>
       <c r="E868" s="3"/>
       <c r="F868" s="3"/>
       <c r="G868" s="3"/>
@@ -22596,7 +22620,7 @@
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
-      <c r="D869" s="33"/>
+      <c r="D869" s="39"/>
       <c r="E869" s="3"/>
       <c r="F869" s="3"/>
       <c r="G869" s="3"/>
@@ -22621,7 +22645,7 @@
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
-      <c r="D870" s="33"/>
+      <c r="D870" s="39"/>
       <c r="E870" s="3"/>
       <c r="F870" s="3"/>
       <c r="G870" s="3"/>
@@ -22646,7 +22670,7 @@
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
-      <c r="D871" s="33"/>
+      <c r="D871" s="39"/>
       <c r="E871" s="3"/>
       <c r="F871" s="3"/>
       <c r="G871" s="3"/>
@@ -22671,7 +22695,7 @@
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
-      <c r="D872" s="33"/>
+      <c r="D872" s="39"/>
       <c r="E872" s="3"/>
       <c r="F872" s="3"/>
       <c r="G872" s="3"/>
@@ -22696,7 +22720,7 @@
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
-      <c r="D873" s="33"/>
+      <c r="D873" s="39"/>
       <c r="E873" s="3"/>
       <c r="F873" s="3"/>
       <c r="G873" s="3"/>
@@ -22721,7 +22745,7 @@
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
-      <c r="D874" s="33"/>
+      <c r="D874" s="39"/>
       <c r="E874" s="3"/>
       <c r="F874" s="3"/>
       <c r="G874" s="3"/>
@@ -22746,7 +22770,7 @@
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
-      <c r="D875" s="33"/>
+      <c r="D875" s="39"/>
       <c r="E875" s="3"/>
       <c r="F875" s="3"/>
       <c r="G875" s="3"/>
@@ -22771,7 +22795,7 @@
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
-      <c r="D876" s="33"/>
+      <c r="D876" s="39"/>
       <c r="E876" s="3"/>
       <c r="F876" s="3"/>
       <c r="G876" s="3"/>
@@ -22796,7 +22820,7 @@
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
-      <c r="D877" s="33"/>
+      <c r="D877" s="39"/>
       <c r="E877" s="3"/>
       <c r="F877" s="3"/>
       <c r="G877" s="3"/>
@@ -22821,7 +22845,7 @@
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
-      <c r="D878" s="33"/>
+      <c r="D878" s="39"/>
       <c r="E878" s="3"/>
       <c r="F878" s="3"/>
       <c r="G878" s="3"/>
@@ -22846,7 +22870,7 @@
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
-      <c r="D879" s="33"/>
+      <c r="D879" s="39"/>
       <c r="E879" s="3"/>
       <c r="F879" s="3"/>
       <c r="G879" s="3"/>
@@ -22871,7 +22895,7 @@
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
-      <c r="D880" s="33"/>
+      <c r="D880" s="39"/>
       <c r="E880" s="3"/>
       <c r="F880" s="3"/>
       <c r="G880" s="3"/>
@@ -22896,7 +22920,7 @@
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
-      <c r="D881" s="33"/>
+      <c r="D881" s="39"/>
       <c r="E881" s="3"/>
       <c r="F881" s="3"/>
       <c r="G881" s="3"/>
@@ -22921,7 +22945,7 @@
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
-      <c r="D882" s="33"/>
+      <c r="D882" s="39"/>
       <c r="E882" s="3"/>
       <c r="F882" s="3"/>
       <c r="G882" s="3"/>
@@ -22946,7 +22970,7 @@
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
-      <c r="D883" s="33"/>
+      <c r="D883" s="39"/>
       <c r="E883" s="3"/>
       <c r="F883" s="3"/>
       <c r="G883" s="3"/>
@@ -22971,7 +22995,7 @@
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
-      <c r="D884" s="33"/>
+      <c r="D884" s="39"/>
       <c r="E884" s="3"/>
       <c r="F884" s="3"/>
       <c r="G884" s="3"/>
@@ -22996,7 +23020,7 @@
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
-      <c r="D885" s="33"/>
+      <c r="D885" s="39"/>
       <c r="E885" s="3"/>
       <c r="F885" s="3"/>
       <c r="G885" s="3"/>
@@ -23021,7 +23045,7 @@
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
-      <c r="D886" s="33"/>
+      <c r="D886" s="39"/>
       <c r="E886" s="3"/>
       <c r="F886" s="3"/>
       <c r="G886" s="3"/>
@@ -23046,7 +23070,7 @@
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
-      <c r="D887" s="33"/>
+      <c r="D887" s="39"/>
       <c r="E887" s="3"/>
       <c r="F887" s="3"/>
       <c r="G887" s="3"/>
@@ -23071,7 +23095,7 @@
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
-      <c r="D888" s="33"/>
+      <c r="D888" s="39"/>
       <c r="E888" s="3"/>
       <c r="F888" s="3"/>
       <c r="G888" s="3"/>
@@ -23096,7 +23120,7 @@
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
-      <c r="D889" s="33"/>
+      <c r="D889" s="39"/>
       <c r="E889" s="3"/>
       <c r="F889" s="3"/>
       <c r="G889" s="3"/>
@@ -23121,7 +23145,7 @@
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
-      <c r="D890" s="33"/>
+      <c r="D890" s="39"/>
       <c r="E890" s="3"/>
       <c r="F890" s="3"/>
       <c r="G890" s="3"/>
@@ -23146,7 +23170,7 @@
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
-      <c r="D891" s="33"/>
+      <c r="D891" s="39"/>
       <c r="E891" s="3"/>
       <c r="F891" s="3"/>
       <c r="G891" s="3"/>
@@ -23171,7 +23195,7 @@
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
-      <c r="D892" s="33"/>
+      <c r="D892" s="39"/>
       <c r="E892" s="3"/>
       <c r="F892" s="3"/>
       <c r="G892" s="3"/>
